--- a/templates/NEK_Document_Templates.xlsx
+++ b/templates/NEK_Document_Templates.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timot\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244374C9-7F73-40EF-9E05-8F799ABB3FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6DFFA0-47B3-4B1A-AF00-ADFD727CBB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00 House Style" sheetId="1" r:id="rId1"/>
@@ -664,7 +664,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -912,10 +912,10 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -924,20 +924,24 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -947,34 +951,30 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2119,8 +2119,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="str">
-        <f>IFERROR(INDEX(_EntityData!$B$3:$B$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)),"")</f>
+      <c r="A1" s="40" t="str">
+        <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
       <c r="B1" s="31"/>
@@ -2136,7 +2136,7 @@
       <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="37" t="s">
         <v>127</v>
       </c>
       <c r="B2" s="31"/>
@@ -2146,14 +2146,14 @@
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="30" t="s">
         <v>128</v>
       </c>
       <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="41" t="str">
-        <f>IFERROR(INDEX(_EntityData!$D$3:$D$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)),"")</f>
+      <c r="A3" s="34" t="str">
+        <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
       <c r="B3" s="31"/>
@@ -2171,8 +2171,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="41" t="str">
-        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)))</f>
+      <c r="A4" s="34" t="str">
+        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
       <c r="B4" s="31"/>
@@ -2210,7 +2210,7 @@
         <v>130</v>
       </c>
       <c r="K6" s="16" t="str">
-        <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$13,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$13,0)),"")</f>
+        <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       <c r="A7" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="33" t="s">
         <v>132</v>
       </c>
       <c r="C7" s="31"/>
@@ -2250,7 +2250,7 @@
         <v>137</v>
       </c>
       <c r="K8" s="21" t="str">
-        <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$13,0)),"","! bank code not linked to this entity"))</f>
+        <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
@@ -2263,105 +2263,105 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="36" t="s">
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="36" t="s">
+      <c r="F11" s="39"/>
+      <c r="G11" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="H11" s="37"/>
+      <c r="H11" s="39"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="33" t="s">
         <v>141</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
-      <c r="E12" s="30">
+      <c r="E12" s="35">
         <v>2793</v>
       </c>
       <c r="F12" s="31"/>
-      <c r="G12" s="33"/>
+      <c r="G12" s="36"/>
       <c r="H12" s="31"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="32"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
       <c r="D13" s="31"/>
-      <c r="E13" s="30"/>
+      <c r="E13" s="35"/>
       <c r="F13" s="31"/>
-      <c r="G13" s="33"/>
+      <c r="G13" s="36"/>
       <c r="H13" s="31"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="32"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
       <c r="D14" s="31"/>
-      <c r="E14" s="30"/>
+      <c r="E14" s="35"/>
       <c r="F14" s="31"/>
-      <c r="G14" s="33"/>
+      <c r="G14" s="36"/>
       <c r="H14" s="31"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="32"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="31"/>
       <c r="C15" s="31"/>
       <c r="D15" s="31"/>
-      <c r="E15" s="30"/>
+      <c r="E15" s="35"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="33"/>
+      <c r="G15" s="36"/>
       <c r="H15" s="31"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="32"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="31"/>
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
-      <c r="E16" s="30"/>
+      <c r="E16" s="35"/>
       <c r="F16" s="31"/>
-      <c r="G16" s="33"/>
+      <c r="G16" s="36"/>
       <c r="H16" s="31"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="32"/>
+      <c r="A17" s="33"/>
       <c r="B17" s="31"/>
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
-      <c r="E17" s="30"/>
+      <c r="E17" s="35"/>
       <c r="F17" s="31"/>
-      <c r="G17" s="33"/>
+      <c r="G17" s="36"/>
       <c r="H17" s="31"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="45" t="s">
         <v>142</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
-      <c r="E18" s="45">
+      <c r="E18" s="32">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
       <c r="F18" s="31"/>
-      <c r="G18" s="40"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="31"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="42" t="s">
         <v>144</v>
       </c>
       <c r="C20" s="31"/>
@@ -2375,12 +2375,12 @@
       <c r="A23" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="35"/>
+      <c r="B23" s="41"/>
       <c r="C23" s="31"/>
       <c r="E23" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="F23" s="35"/>
+      <c r="F23" s="41"/>
       <c r="G23" s="31"/>
       <c r="H23" s="31"/>
     </row>
@@ -2388,18 +2388,18 @@
       <c r="A25" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B25" s="35"/>
+      <c r="B25" s="41"/>
       <c r="C25" s="31"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B27" s="35"/>
+      <c r="B27" s="41"/>
       <c r="C27" s="31"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="34" t="s">
+      <c r="A30" s="44" t="s">
         <v>149</v>
       </c>
       <c r="B30" s="31"/>
@@ -2412,19 +2412,12 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="E17:F17"/>
@@ -2441,13 +2434,20 @@
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A17:D17"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -2491,8 +2491,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="str">
-        <f>IFERROR(INDEX(_EntityData!$B$3:$B$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)),"")</f>
+      <c r="A1" s="40" t="str">
+        <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
       <c r="B1" s="31"/>
@@ -2508,7 +2508,7 @@
       <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="37" t="s">
         <v>150</v>
       </c>
       <c r="B2" s="31"/>
@@ -2518,14 +2518,14 @@
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="30" t="s">
         <v>128</v>
       </c>
       <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="41" t="str">
-        <f>IFERROR(INDEX(_EntityData!$D$3:$D$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)),"")</f>
+      <c r="A3" s="34" t="str">
+        <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
       <c r="B3" s="31"/>
@@ -2543,8 +2543,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="41" t="str">
-        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)))</f>
+      <c r="A4" s="34" t="str">
+        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
       <c r="B4" s="31"/>
@@ -2582,7 +2582,7 @@
         <v>130</v>
       </c>
       <c r="K6" s="16" t="str">
-        <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$13,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$13,0)),"")</f>
+        <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       <c r="A7" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="33" t="s">
         <v>132</v>
       </c>
       <c r="C7" s="31"/>
@@ -2622,7 +2622,7 @@
         <v>137</v>
       </c>
       <c r="K8" s="21" t="str">
-        <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$13,0)),"","! bank code not linked to this entity"))</f>
+        <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
@@ -2635,105 +2635,105 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="36" t="s">
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="36" t="s">
+      <c r="F11" s="39"/>
+      <c r="G11" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="H11" s="37"/>
+      <c r="H11" s="39"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="33" t="s">
         <v>141</v>
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
-      <c r="E12" s="30">
+      <c r="E12" s="35">
         <v>2793</v>
       </c>
       <c r="F12" s="31"/>
-      <c r="G12" s="33"/>
+      <c r="G12" s="36"/>
       <c r="H12" s="31"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="32"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
       <c r="D13" s="31"/>
-      <c r="E13" s="30"/>
+      <c r="E13" s="35"/>
       <c r="F13" s="31"/>
-      <c r="G13" s="33"/>
+      <c r="G13" s="36"/>
       <c r="H13" s="31"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="32"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
       <c r="D14" s="31"/>
-      <c r="E14" s="30"/>
+      <c r="E14" s="35"/>
       <c r="F14" s="31"/>
-      <c r="G14" s="33"/>
+      <c r="G14" s="36"/>
       <c r="H14" s="31"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="32"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="31"/>
       <c r="C15" s="31"/>
       <c r="D15" s="31"/>
-      <c r="E15" s="30"/>
+      <c r="E15" s="35"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="33"/>
+      <c r="G15" s="36"/>
       <c r="H15" s="31"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="32"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="31"/>
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
-      <c r="E16" s="30"/>
+      <c r="E16" s="35"/>
       <c r="F16" s="31"/>
-      <c r="G16" s="33"/>
+      <c r="G16" s="36"/>
       <c r="H16" s="31"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="32"/>
+      <c r="A17" s="33"/>
       <c r="B17" s="31"/>
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
-      <c r="E17" s="30"/>
+      <c r="E17" s="35"/>
       <c r="F17" s="31"/>
-      <c r="G17" s="33"/>
+      <c r="G17" s="36"/>
       <c r="H17" s="31"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="45" t="s">
         <v>142</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
-      <c r="E18" s="45">
+      <c r="E18" s="32">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
       <c r="F18" s="31"/>
-      <c r="G18" s="40"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="31"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="42" t="s">
         <v>144</v>
       </c>
       <c r="C20" s="31"/>
@@ -2747,12 +2747,12 @@
       <c r="A23" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="35"/>
+      <c r="B23" s="41"/>
       <c r="C23" s="31"/>
       <c r="E23" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="F23" s="35"/>
+      <c r="F23" s="41"/>
       <c r="G23" s="31"/>
       <c r="H23" s="31"/>
     </row>
@@ -2760,18 +2760,18 @@
       <c r="A25" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B25" s="35"/>
+      <c r="B25" s="41"/>
       <c r="C25" s="31"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B27" s="35"/>
+      <c r="B27" s="41"/>
       <c r="C27" s="31"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="34" t="s">
+      <c r="A30" s="44" t="s">
         <v>149</v>
       </c>
       <c r="B30" s="31"/>
@@ -2784,19 +2784,12 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="E17:F17"/>
@@ -2813,13 +2806,20 @@
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A17:D17"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0400-000001000000}">
@@ -2863,8 +2863,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="str">
-        <f>IFERROR(INDEX(_EntityData!$B$3:$B$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)),"")</f>
+      <c r="A1" s="40" t="str">
+        <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
       <c r="B1" s="31"/>
@@ -2880,7 +2880,7 @@
       <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="37" t="s">
         <v>153</v>
       </c>
       <c r="B2" s="31"/>
@@ -2890,14 +2890,14 @@
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="30" t="s">
         <v>128</v>
       </c>
       <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="41" t="str">
-        <f>IFERROR(INDEX(_EntityData!$D$3:$D$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)),"")</f>
+      <c r="A3" s="34" t="str">
+        <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
       <c r="B3" s="31"/>
@@ -2915,8 +2915,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="41" t="str">
-        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)))</f>
+      <c r="A4" s="34" t="str">
+        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
       <c r="B4" s="31"/>
@@ -2954,7 +2954,7 @@
         <v>130</v>
       </c>
       <c r="K6" s="16" t="str">
-        <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$13,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$13,0)),"")</f>
+        <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Malayan Banking Berhad (Maybank)</v>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="33" t="s">
         <v>132</v>
       </c>
       <c r="B8" s="31"/>
@@ -2995,12 +2995,12 @@
         <v>137</v>
       </c>
       <c r="K8" s="21" t="str">
-        <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$13,0)),"","! bank code not linked to this entity"))</f>
+        <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="46" t="s">
         <v>156</v>
       </c>
       <c r="B9" s="31"/>
@@ -3009,89 +3009,89 @@
       <c r="E9" s="31"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="36" t="s">
+      <c r="B11" s="39"/>
+      <c r="C11" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="36" t="s">
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="H11" s="37"/>
+      <c r="H11" s="39"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="33">
+      <c r="A12" s="36">
         <v>1</v>
       </c>
       <c r="B12" s="31"/>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="33" t="s">
         <v>160</v>
       </c>
       <c r="D12" s="31"/>
       <c r="E12" s="31"/>
       <c r="F12" s="31"/>
-      <c r="G12" s="30">
+      <c r="G12" s="35">
         <v>9000</v>
       </c>
       <c r="H12" s="31"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="33"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="31"/>
-      <c r="C13" s="32"/>
+      <c r="C13" s="33"/>
       <c r="D13" s="31"/>
       <c r="E13" s="31"/>
       <c r="F13" s="31"/>
-      <c r="G13" s="30"/>
+      <c r="G13" s="35"/>
       <c r="H13" s="31"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="33"/>
+      <c r="A14" s="36"/>
       <c r="B14" s="31"/>
-      <c r="C14" s="32"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
-      <c r="G14" s="30"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="31"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="33"/>
+      <c r="A15" s="36"/>
       <c r="B15" s="31"/>
-      <c r="C15" s="32"/>
+      <c r="C15" s="33"/>
       <c r="D15" s="31"/>
       <c r="E15" s="31"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="30"/>
+      <c r="G15" s="35"/>
       <c r="H15" s="31"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="33"/>
+      <c r="A16" s="36"/>
       <c r="B16" s="31"/>
-      <c r="C16" s="32"/>
+      <c r="C16" s="33"/>
       <c r="D16" s="31"/>
       <c r="E16" s="31"/>
       <c r="F16" s="31"/>
-      <c r="G16" s="30"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="31"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="31"/>
-      <c r="C17" s="32"/>
+      <c r="C17" s="33"/>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
       <c r="F17" s="31"/>
-      <c r="G17" s="30"/>
+      <c r="G17" s="35"/>
       <c r="H17" s="31"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="45" t="s">
         <v>161</v>
       </c>
       <c r="B18" s="31"/>
@@ -3099,7 +3099,7 @@
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
       <c r="F18" s="31"/>
-      <c r="G18" s="45">
+      <c r="G18" s="32">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
@@ -3109,7 +3109,7 @@
       <c r="A20" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="42" t="s">
         <v>144</v>
       </c>
       <c r="C20" s="31"/>
@@ -3120,7 +3120,7 @@
       <c r="H20" s="31"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="47" t="s">
         <v>162</v>
       </c>
       <c r="B22" s="31"/>
@@ -3132,8 +3132,8 @@
       <c r="H22" s="31"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="46" t="str">
-        <f>IF($K$3="","","Bank : "&amp;IFERROR(INDEX(_BankAccounts!$D$3:$D$13,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$13,0)),""))</f>
+      <c r="A23" s="47" t="str">
+        <f>IF($K$3="","","Bank : "&amp;IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),""))</f>
         <v>Bank : Malayan Banking Berhad (Maybank)</v>
       </c>
       <c r="B23" s="31"/>
@@ -3145,7 +3145,7 @@
       <c r="H23" s="31"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="44" t="s">
         <v>163</v>
       </c>
       <c r="B25" s="31"/>
@@ -3158,25 +3158,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="G17:H17"/>
@@ -3192,6 +3173,25 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0500-000001000000}">
@@ -3235,8 +3235,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="str">
-        <f>IFERROR(INDEX(_EntityData!$B$3:$B$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)),"")</f>
+      <c r="A1" s="40" t="str">
+        <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
       <c r="B1" s="31"/>
@@ -3252,7 +3252,7 @@
       <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="37" t="s">
         <v>164</v>
       </c>
       <c r="B2" s="31"/>
@@ -3262,14 +3262,14 @@
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="30" t="s">
         <v>128</v>
       </c>
       <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="41" t="str">
-        <f>IFERROR(INDEX(_EntityData!$D$3:$D$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)),"")</f>
+      <c r="A3" s="34" t="str">
+        <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
       <c r="B3" s="31"/>
@@ -3287,8 +3287,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="41" t="str">
-        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)))</f>
+      <c r="A4" s="34" t="str">
+        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
       <c r="B4" s="31"/>
@@ -3326,7 +3326,7 @@
         <v>130</v>
       </c>
       <c r="K6" s="16" t="str">
-        <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$13,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$13,0)),"")</f>
+        <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="33" t="s">
         <v>132</v>
       </c>
       <c r="B8" s="31"/>
@@ -3367,12 +3367,12 @@
         <v>137</v>
       </c>
       <c r="K8" s="21" t="str">
-        <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$13,0)),"","! bank code not linked to this entity"))</f>
+        <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="46" t="s">
         <v>156</v>
       </c>
       <c r="B9" s="31"/>
@@ -3381,89 +3381,89 @@
       <c r="E9" s="31"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="36" t="s">
+      <c r="B11" s="39"/>
+      <c r="C11" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="36" t="s">
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="H11" s="37"/>
+      <c r="H11" s="39"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="33">
+      <c r="A12" s="36">
         <v>1</v>
       </c>
       <c r="B12" s="31"/>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="33" t="s">
         <v>160</v>
       </c>
       <c r="D12" s="31"/>
       <c r="E12" s="31"/>
       <c r="F12" s="31"/>
-      <c r="G12" s="30">
+      <c r="G12" s="35">
         <v>9000</v>
       </c>
       <c r="H12" s="31"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="33"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="31"/>
-      <c r="C13" s="32"/>
+      <c r="C13" s="33"/>
       <c r="D13" s="31"/>
       <c r="E13" s="31"/>
       <c r="F13" s="31"/>
-      <c r="G13" s="30"/>
+      <c r="G13" s="35"/>
       <c r="H13" s="31"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="33"/>
+      <c r="A14" s="36"/>
       <c r="B14" s="31"/>
-      <c r="C14" s="32"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
-      <c r="G14" s="30"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="31"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="33"/>
+      <c r="A15" s="36"/>
       <c r="B15" s="31"/>
-      <c r="C15" s="32"/>
+      <c r="C15" s="33"/>
       <c r="D15" s="31"/>
       <c r="E15" s="31"/>
       <c r="F15" s="31"/>
-      <c r="G15" s="30"/>
+      <c r="G15" s="35"/>
       <c r="H15" s="31"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="33"/>
+      <c r="A16" s="36"/>
       <c r="B16" s="31"/>
-      <c r="C16" s="32"/>
+      <c r="C16" s="33"/>
       <c r="D16" s="31"/>
       <c r="E16" s="31"/>
       <c r="F16" s="31"/>
-      <c r="G16" s="30"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="31"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="33"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="31"/>
-      <c r="C17" s="32"/>
+      <c r="C17" s="33"/>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
       <c r="F17" s="31"/>
-      <c r="G17" s="30"/>
+      <c r="G17" s="35"/>
       <c r="H17" s="31"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="45" t="s">
         <v>161</v>
       </c>
       <c r="B18" s="31"/>
@@ -3471,7 +3471,7 @@
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
       <c r="F18" s="31"/>
-      <c r="G18" s="45">
+      <c r="G18" s="32">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
@@ -3481,7 +3481,7 @@
       <c r="A20" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="42" t="s">
         <v>144</v>
       </c>
       <c r="C20" s="31"/>
@@ -3506,8 +3506,8 @@
       <c r="A23" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C23" s="48" t="str">
-        <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$13,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$13,0)),"")</f>
+      <c r="C23" s="50" t="str">
+        <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
       <c r="D23" s="31"/>
@@ -3526,7 +3526,7 @@
       <c r="F24" s="31"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="50" t="s">
+      <c r="A26" s="48" t="s">
         <v>172</v>
       </c>
       <c r="B26" s="31"/>
@@ -3538,7 +3538,7 @@
       <c r="H26" s="31"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="44" t="s">
         <v>163</v>
       </c>
       <c r="B28" s="31"/>
@@ -3551,6 +3551,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="A28:H28"/>
@@ -3567,26 +3587,6 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0600-000001000000}">
@@ -3630,8 +3630,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="str">
-        <f>IFERROR(INDEX(_EntityData!$B$3:$B$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)),"")</f>
+      <c r="A1" s="40" t="str">
+        <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
       <c r="B1" s="31"/>
@@ -3646,7 +3646,7 @@
       <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="37" t="s">
         <v>173</v>
       </c>
       <c r="B2" s="31"/>
@@ -3655,14 +3655,14 @@
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="30" t="s">
         <v>128</v>
       </c>
       <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="41" t="str">
-        <f>IFERROR(INDEX(_EntityData!$D$3:$D$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)),"")</f>
+      <c r="A3" s="34" t="str">
+        <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
       <c r="B3" s="31"/>
@@ -3679,8 +3679,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="41" t="str">
-        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$13,MATCH($K$3,_EntityData!$A$3:$A$13,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$13,MATCH($K$3,_EntityData!$A$3:$A$13,0)))</f>
+      <c r="A4" s="34" t="str">
+        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
       <c r="B4" s="31"/>
@@ -3716,7 +3716,7 @@
         <v>130</v>
       </c>
       <c r="K6" s="16" t="str">
-        <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$13,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$13,0)),"")</f>
+        <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       <c r="E8" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="36" t="s">
         <v>63</v>
       </c>
       <c r="G8" s="31"/>
@@ -3762,7 +3762,7 @@
         <v>137</v>
       </c>
       <c r="K8" s="21" t="str">
-        <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$13,0)),"","! bank code not linked to this entity"))</f>
+        <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="44" t="s">
         <v>202</v>
       </c>
       <c r="B29" s="31"/>
@@ -3997,6 +3997,10 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A3:G3"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
@@ -4008,10 +4012,6 @@
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="E10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A3:G3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0700-000001000000}">

--- a/templates/NEK_Document_Templates.xlsx
+++ b/templates/NEK_Document_Templates.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6DFFA0-47B3-4B1A-AF00-ADFD727CBB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D69523B-772F-4EBF-8234-717598B35D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00 House Style" sheetId="1" r:id="rId1"/>
-    <sheet name="_EntityData" sheetId="2" r:id="rId2"/>
-    <sheet name="_BankAccounts" sheetId="3" r:id="rId3"/>
-    <sheet name="Payment Voucher" sheetId="4" r:id="rId4"/>
-    <sheet name="Receiving Voucher" sheetId="5" r:id="rId5"/>
-    <sheet name="Invoice" sheetId="6" r:id="rId6"/>
-    <sheet name="Official Receipt" sheetId="7" r:id="rId7"/>
-    <sheet name="Salary Slip" sheetId="8" r:id="rId8"/>
+    <sheet name="_Currency" sheetId="9" state="veryHidden" r:id="rId2"/>
+    <sheet name="_EntityData" sheetId="2" r:id="rId3"/>
+    <sheet name="_BankAccounts" sheetId="3" r:id="rId4"/>
+    <sheet name="Payment Voucher" sheetId="4" r:id="rId5"/>
+    <sheet name="Receiving Voucher" sheetId="5" r:id="rId6"/>
+    <sheet name="Invoice" sheetId="6" r:id="rId7"/>
+    <sheet name="Official Receipt" sheetId="7" r:id="rId8"/>
+    <sheet name="Salary Slip" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">Invoice!$A$1:$H$25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Official Receipt'!$A$1:$H$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Payment Voucher'!$A$1:$H$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Receiving Voucher'!$A$1:$H$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Salary Slip'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">Invoice!$A$1:$H$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Official Receipt'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Payment Voucher'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Receiving Voucher'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Salary Slip'!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="211">
   <si>
     <t>NEK GROUP — DOCUMENT HOUSE STYLE</t>
   </si>
@@ -478,9 +479,6 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Ringgit Malaysia :</t>
-  </si>
-  <si>
     <t>[amount in words]</t>
   </si>
   <si>
@@ -526,9 +524,6 @@
     <t>DESCRIPTION</t>
   </si>
   <si>
-    <t>AMOUNT (MYR)</t>
-  </si>
-  <si>
     <t>RENTAL (July 2026) — 1G-10-03, Andaman Quayside</t>
   </si>
   <si>
@@ -656,6 +651,36 @@
   </si>
   <si>
     <t>This is a computer-generated payslip. No signature is required. For payroll record purposes only.</t>
+  </si>
+  <si>
+    <t>CURRENCY WORDING - written from scripts/amount_in_words.py on every run. Do not hand-edit; the script is the source.</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Major Unit</t>
+  </si>
+  <si>
+    <t>Minor Unit</t>
+  </si>
+  <si>
+    <t>Hong Kong Dollars</t>
+  </si>
+  <si>
+    <t>Cents</t>
+  </si>
+  <si>
+    <t>Ringgit Malaysia</t>
+  </si>
+  <si>
+    <t>Sen</t>
+  </si>
+  <si>
+    <t>US Dollars</t>
+  </si>
+  <si>
+    <t>Currency (auto)</t>
   </si>
 </sst>
 </file>
@@ -924,16 +949,18 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -941,44 +968,42 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1508,6 +1533,65 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41A8F3C5-CF39-4D34-8F9F-443C84977BAE}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1799,7 +1883,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2099,7 +2183,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2119,7 +2203,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="str">
+      <c r="A1" s="37" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
@@ -2136,7 +2220,7 @@
       <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="45" t="s">
         <v>127</v>
       </c>
       <c r="B2" s="31"/>
@@ -2146,13 +2230,13 @@
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="42" t="s">
         <v>128</v>
       </c>
       <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="str">
+      <c r="A3" s="44" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
@@ -2171,7 +2255,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="34" t="str">
+      <c r="A4" s="44" t="str">
         <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
@@ -2261,22 +2345,30 @@
       <c r="H9" s="22">
         <v>46228</v>
       </c>
+      <c r="J9" t="s">
+        <v>210</v>
+      </c>
+      <c r="K9" t="str">
+        <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
+        <v>MYR</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="38" t="s">
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="39" t="str">
+        <f>$K$9</f>
+        <v>MYR</v>
+      </c>
+      <c r="F11" s="40"/>
+      <c r="G11" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="H11" s="39"/>
+      <c r="H11" s="40"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="33" t="s">
@@ -2343,26 +2435,27 @@
       <c r="H17" s="31"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="34" t="s">
         <v>142</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
-      <c r="E18" s="32">
+      <c r="E18" s="43">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
       <c r="F18" s="31"/>
-      <c r="G18" s="43"/>
+      <c r="G18" s="41"/>
       <c r="H18" s="31"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="4" t="str">
+        <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
+        <v>Ringgit Malaysia :</v>
+      </c>
+      <c r="B20" s="38" t="s">
         <v>143</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>144</v>
       </c>
       <c r="C20" s="31"/>
       <c r="D20" s="31"/>
@@ -2373,34 +2466,34 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" s="41"/>
+        <v>144</v>
+      </c>
+      <c r="B23" s="32"/>
       <c r="C23" s="31"/>
       <c r="E23" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="F23" s="41"/>
+        <v>145</v>
+      </c>
+      <c r="F23" s="32"/>
       <c r="G23" s="31"/>
       <c r="H23" s="31"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="B25" s="41"/>
+        <v>146</v>
+      </c>
+      <c r="B25" s="32"/>
       <c r="C25" s="31"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" s="32"/>
+      <c r="C27" s="31"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="30" t="s">
         <v>148</v>
-      </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="31"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="44" t="s">
-        <v>149</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
@@ -2412,12 +2505,20 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G12:H12"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="E17:F17"/>
@@ -2434,20 +2535,12 @@
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -2471,7 +2564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2491,7 +2584,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="str">
+      <c r="A1" s="37" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
@@ -2508,8 +2601,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
-        <v>150</v>
+      <c r="A2" s="45" t="s">
+        <v>149</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -2518,13 +2611,13 @@
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="42" t="s">
         <v>128</v>
       </c>
       <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="str">
+      <c r="A3" s="44" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
@@ -2543,7 +2636,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="34" t="str">
+      <c r="A4" s="44" t="str">
         <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
@@ -2588,7 +2681,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B7" s="33" t="s">
         <v>132</v>
@@ -2597,7 +2690,7 @@
       <c r="D7" s="31"/>
       <c r="E7" s="31"/>
       <c r="G7" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H7" s="18" t="str">
         <f>K7</f>
@@ -2633,22 +2726,30 @@
       <c r="H9" s="22">
         <v>46228</v>
       </c>
+      <c r="J9" t="s">
+        <v>210</v>
+      </c>
+      <c r="K9" t="str">
+        <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
+        <v>MYR</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="38" t="s">
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="39" t="str">
+        <f>$K$9</f>
+        <v>MYR</v>
+      </c>
+      <c r="F11" s="40"/>
+      <c r="G11" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="H11" s="39"/>
+      <c r="H11" s="40"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="33" t="s">
@@ -2715,26 +2816,27 @@
       <c r="H17" s="31"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="34" t="s">
         <v>142</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
-      <c r="E18" s="32">
+      <c r="E18" s="43">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
       <c r="F18" s="31"/>
-      <c r="G18" s="43"/>
+      <c r="G18" s="41"/>
       <c r="H18" s="31"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="4" t="str">
+        <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
+        <v>Ringgit Malaysia :</v>
+      </c>
+      <c r="B20" s="38" t="s">
         <v>143</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>144</v>
       </c>
       <c r="C20" s="31"/>
       <c r="D20" s="31"/>
@@ -2745,34 +2847,34 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" s="41"/>
+        <v>144</v>
+      </c>
+      <c r="B23" s="32"/>
       <c r="C23" s="31"/>
       <c r="E23" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="F23" s="41"/>
+        <v>145</v>
+      </c>
+      <c r="F23" s="32"/>
       <c r="G23" s="31"/>
       <c r="H23" s="31"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="B25" s="41"/>
+        <v>146</v>
+      </c>
+      <c r="B25" s="32"/>
       <c r="C25" s="31"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" s="32"/>
+      <c r="C27" s="31"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="30" t="s">
         <v>148</v>
-      </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="31"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="44" t="s">
-        <v>149</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
@@ -2784,12 +2886,20 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G12:H12"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="E17:F17"/>
@@ -2806,20 +2916,12 @@
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0400-000001000000}">
@@ -2843,7 +2945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2863,7 +2965,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="str">
+      <c r="A1" s="37" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
@@ -2880,8 +2982,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
-        <v>153</v>
+      <c r="A2" s="45" t="s">
+        <v>152</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -2890,13 +2992,13 @@
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="42" t="s">
         <v>128</v>
       </c>
       <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="str">
+      <c r="A3" s="44" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
@@ -2915,7 +3017,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="34" t="str">
+      <c r="A4" s="44" t="str">
         <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
@@ -2960,10 +3062,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>154</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>155</v>
       </c>
       <c r="H7" s="18" t="str">
         <f>K7</f>
@@ -3000,29 +3102,37 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="46" t="s">
-        <v>156</v>
+      <c r="A9" s="47" t="s">
+        <v>155</v>
       </c>
       <c r="B9" s="31"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="E9" s="31"/>
+      <c r="J9" t="s">
+        <v>210</v>
+      </c>
+      <c r="K9" t="str">
+        <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
+        <v>MYR</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="H11" s="39"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="39" t="str">
+        <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
+        <v>AMOUNT (MYR)</v>
+      </c>
+      <c r="H11" s="40"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="36">
@@ -3030,7 +3140,7 @@
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="33" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" s="31"/>
       <c r="E12" s="31"/>
@@ -3091,26 +3201,27 @@
       <c r="H17" s="31"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="45" t="s">
-        <v>161</v>
+      <c r="A18" s="34" t="s">
+        <v>159</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
       <c r="F18" s="31"/>
-      <c r="G18" s="32">
+      <c r="G18" s="43">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
       <c r="H18" s="31"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="4" t="str">
+        <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
+        <v>Ringgit Malaysia :</v>
+      </c>
+      <c r="B20" s="38" t="s">
         <v>143</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>144</v>
       </c>
       <c r="C20" s="31"/>
       <c r="D20" s="31"/>
@@ -3120,8 +3231,8 @@
       <c r="H20" s="31"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="47" t="s">
-        <v>162</v>
+      <c r="A22" s="46" t="s">
+        <v>160</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="31"/>
@@ -3132,7 +3243,7 @@
       <c r="H22" s="31"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="47" t="str">
+      <c r="A23" s="46" t="str">
         <f>IF($K$3="","","Bank : "&amp;IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),""))</f>
         <v>Bank : Malayan Banking Berhad (Maybank)</v>
       </c>
@@ -3145,8 +3256,8 @@
       <c r="H23" s="31"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="44" t="s">
-        <v>163</v>
+      <c r="A25" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
@@ -3158,6 +3269,25 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="G17:H17"/>
@@ -3173,25 +3303,6 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0500-000001000000}">
@@ -3215,7 +3326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3235,7 +3346,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="str">
+      <c r="A1" s="37" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
@@ -3252,8 +3363,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
-        <v>164</v>
+      <c r="A2" s="45" t="s">
+        <v>162</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -3262,13 +3373,13 @@
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="42" t="s">
         <v>128</v>
       </c>
       <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="str">
+      <c r="A3" s="44" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
@@ -3287,7 +3398,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="34" t="str">
+      <c r="A4" s="44" t="str">
         <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
@@ -3332,10 +3443,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H7" s="18" t="str">
         <f>K7</f>
@@ -3372,29 +3483,37 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="46" t="s">
-        <v>156</v>
+      <c r="A9" s="47" t="s">
+        <v>155</v>
       </c>
       <c r="B9" s="31"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="E9" s="31"/>
+      <c r="J9" t="s">
+        <v>210</v>
+      </c>
+      <c r="K9" t="str">
+        <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
+        <v>MYR</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="H11" s="39"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="39" t="str">
+        <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
+        <v>AMOUNT (MYR)</v>
+      </c>
+      <c r="H11" s="40"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="36">
@@ -3402,7 +3521,7 @@
       </c>
       <c r="B12" s="31"/>
       <c r="C12" s="33" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" s="31"/>
       <c r="E12" s="31"/>
@@ -3463,26 +3582,27 @@
       <c r="H17" s="31"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="45" t="s">
-        <v>161</v>
+      <c r="A18" s="34" t="s">
+        <v>159</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
       <c r="F18" s="31"/>
-      <c r="G18" s="32">
+      <c r="G18" s="43">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
       <c r="H18" s="31"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="4" t="str">
+        <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
+        <v>Ringgit Malaysia :</v>
+      </c>
+      <c r="B20" s="38" t="s">
         <v>143</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>144</v>
       </c>
       <c r="C20" s="31"/>
       <c r="D20" s="31"/>
@@ -3493,10 +3613,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22" s="49" t="s">
-        <v>168</v>
+        <v>165</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>166</v>
       </c>
       <c r="D22" s="31"/>
       <c r="E22" s="31"/>
@@ -3504,9 +3624,9 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C23" s="50" t="str">
+        <v>167</v>
+      </c>
+      <c r="C23" s="49" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
@@ -3516,18 +3636,18 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C24" s="49" t="s">
-        <v>171</v>
+        <v>168</v>
+      </c>
+      <c r="C24" s="48" t="s">
+        <v>169</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="48" t="s">
-        <v>172</v>
+      <c r="A26" s="50" t="s">
+        <v>170</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
@@ -3538,8 +3658,8 @@
       <c r="H26" s="31"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="44" t="s">
-        <v>163</v>
+      <c r="A28" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="B28" s="31"/>
       <c r="C28" s="31"/>
@@ -3551,26 +3671,6 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C23:F23"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="A28:H28"/>
@@ -3587,6 +3687,26 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0600-000001000000}">
@@ -3610,7 +3730,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3630,7 +3750,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="str">
+      <c r="A1" s="37" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
@@ -3646,8 +3766,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
-        <v>173</v>
+      <c r="A2" s="45" t="s">
+        <v>171</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -3655,13 +3775,13 @@
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="42" t="s">
         <v>128</v>
       </c>
       <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="str">
+      <c r="A3" s="44" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
@@ -3679,7 +3799,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="34" t="str">
+      <c r="A4" s="44" t="str">
         <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
@@ -3722,17 +3842,17 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B7" s="49" t="s">
-        <v>175</v>
+        <v>172</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>173</v>
       </c>
       <c r="C7" s="31"/>
       <c r="E7" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F7" s="49" t="s">
-        <v>177</v>
+        <v>174</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>175</v>
       </c>
       <c r="G7" s="31"/>
       <c r="J7" s="15" t="s">
@@ -3745,14 +3865,14 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B8" s="49" t="s">
-        <v>179</v>
+        <v>176</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>177</v>
       </c>
       <c r="C8" s="31"/>
       <c r="E8" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F8" s="36" t="s">
         <v>63</v>
@@ -3768,35 +3888,35 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="E9" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="F9" s="52" t="str">
+        <v>179</v>
+      </c>
+      <c r="F9" s="51" t="str">
         <f>K7</f>
         <v>SAL/NEK/BOC/202607/014</v>
       </c>
       <c r="G9" s="31"/>
       <c r="J9" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K9" s="23">
         <v>46228</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="51" t="s">
-        <v>183</v>
+      <c r="A10" s="52" t="s">
+        <v>181</v>
       </c>
       <c r="B10" s="31"/>
       <c r="C10" s="31"/>
-      <c r="E10" s="51" t="s">
-        <v>184</v>
+      <c r="E10" s="52" t="s">
+        <v>182</v>
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="31"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="24" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>63</v>
@@ -3805,7 +3925,7 @@
         <v>6500</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F11" s="24" t="s">
         <v>63</v>
@@ -3816,7 +3936,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>63</v>
@@ -3825,7 +3945,7 @@
         <v>300</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F12" s="24" t="s">
         <v>63</v>
@@ -3836,7 +3956,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="E13" s="24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F13" s="24" t="s">
         <v>63</v>
@@ -3847,7 +3967,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>63</v>
@@ -3857,7 +3977,7 @@
         <v>6800</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>63</v>
@@ -3868,15 +3988,15 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="51" t="s">
-        <v>192</v>
+      <c r="A16" s="52" t="s">
+        <v>190</v>
       </c>
       <c r="B16" s="31"/>
       <c r="C16" s="31"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>63</v>
@@ -3887,7 +4007,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>63</v>
@@ -3898,7 +4018,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="24" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>63</v>
@@ -3909,7 +4029,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="24" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>63</v>
@@ -3920,7 +4040,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>63</v>
@@ -3931,7 +4051,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>63</v>
@@ -3942,15 +4062,15 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="51" t="s">
-        <v>199</v>
+      <c r="A24" s="52" t="s">
+        <v>197</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B25" t="s">
         <v>63</v>
@@ -3962,7 +4082,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B26" t="s">
         <v>63</v>
@@ -3974,7 +4094,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="28" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B27" s="28" t="s">
         <v>63</v>
@@ -3985,8 +4105,8 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="44" t="s">
-        <v>202</v>
+      <c r="A29" s="30" t="s">
+        <v>200</v>
       </c>
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
@@ -3997,13 +4117,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="A24:C24"/>
@@ -4012,6 +4125,13 @@
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="E10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0700-000001000000}">

--- a/templates/NEK_Document_Templates.xlsx
+++ b/templates/NEK_Document_Templates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D69523B-772F-4EBF-8234-717598B35D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB8F017-6792-42FD-BF48-4C6E537ECBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -455,9 +455,6 @@
     <t>Reference (auto)</t>
   </si>
   <si>
-    <t>TT / CHEQUE :</t>
-  </si>
-  <si>
     <t>IBG</t>
   </si>
   <si>
@@ -681,6 +678,9 @@
   </si>
   <si>
     <t>Currency (auto)</t>
+  </si>
+  <si>
+    <t>Mode of Payment :</t>
   </si>
 </sst>
 </file>
@@ -762,13 +762,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -823,6 +816,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -847,7 +847,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -888,11 +888,239 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -911,30 +1139,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -947,63 +1171,125 @@
     <xf numFmtId="43" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1539,18 +1825,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" t="s">
         <v>202</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>203</v>
-      </c>
-      <c r="C2" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1558,10 +1844,10 @@
         <v>90</v>
       </c>
       <c r="B3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" t="s">
         <v>205</v>
-      </c>
-      <c r="C3" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1569,10 +1855,10 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" t="s">
         <v>207</v>
-      </c>
-      <c r="C4" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1580,10 +1866,10 @@
         <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2207,65 +2493,66 @@
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="J1" s="10" t="s">
         <v>126</v>
       </c>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="45" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="J2" s="42" t="s">
+    <row r="2" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="32" t="str">
+        <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
+        <v>Co. Reg. No. 198401003022 (115540-H)</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="J2" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="31"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="44" t="str">
+      <c r="K2" s="29"/>
+    </row>
+    <row r="3" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="32" t="str">
+        <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
+        <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="J3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="52" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="J3" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="44" t="str">
-        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
-        <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
-      </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
       <c r="J4" s="12" t="s">
         <v>98</v>
       </c>
@@ -2273,15 +2560,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
+    <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
       <c r="J5" s="12" t="s">
         <v>129</v>
       </c>
@@ -2289,236 +2578,230 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="J6" s="15" t="s">
+    <row r="6" spans="1:11" ht="20.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J6" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="16" t="str">
+      <c r="K6" s="15" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="70" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="G7" s="17" t="s">
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="72"/>
+      <c r="G7" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="H7" s="18" t="str">
+      <c r="H7" s="73" t="str">
         <f>K7</f>
         <v>PV/NEK/BOC/202607/014</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="19" t="str">
+      <c r="K7" s="18" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",H9=""),"","PV/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(H9,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>PV/NEK/BOC/202607/014</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="H8" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="J8" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="J8" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="K8" s="21" t="str">
+      <c r="K8" s="19" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="G9" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="H9" s="22">
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G9" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H9" s="75">
         <v>46228</v>
       </c>
       <c r="J9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K9" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>MYR</v>
       </c>
     </row>
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="39" t="str">
+      <c r="A11" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="63" t="str">
         <f>$K$9</f>
         <v>MYR</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="39" t="s">
+      <c r="F11" s="62"/>
+      <c r="G11" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" s="67"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="60" t="s">
         <v>140</v>
       </c>
-      <c r="H11" s="40"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="33" t="s">
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="58">
+        <v>2793</v>
+      </c>
+      <c r="F12" s="57"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="68"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="60"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="68"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="60"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="68"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="60"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="68"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="60"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="68"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="60"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="68"/>
+    </row>
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="35">
-        <v>2793</v>
-      </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="31"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="33"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="31"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="33"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="31"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="33"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="31"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="33"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="31"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="33"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="31"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="43">
+      <c r="B18" s="65"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="66">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
-      <c r="F18" s="31"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="31"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="69"/>
+    </row>
+    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
+      <c r="B20" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="72"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B23" s="38"/>
+      <c r="C23" s="29"/>
+      <c r="E23" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="31"/>
-      <c r="E23" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="31"/>
+        <v>145</v>
+      </c>
+      <c r="B25" s="38"/>
+      <c r="C25" s="29"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="29"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="31"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G12:H12"/>
+  <mergeCells count="37">
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="E17:F17"/>
@@ -2535,20 +2818,32 @@
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"BOC,BOCOM,MBB,OCBC,TBC,UOB"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8" xr:uid="{FD09BFF1-BCFD-453E-903F-2DC48E0C55F9}">
+      <formula1>"IBG,Cheque,TT"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -2588,65 +2883,66 @@
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="J1" s="10" t="s">
         <v>126</v>
       </c>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="J2" s="42" t="s">
+    <row r="2" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="32" t="str">
+        <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
+        <v>Co. Reg. No. 198401003022 (115540-H)</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="J2" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="31"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="44" t="str">
+      <c r="K2" s="29"/>
+    </row>
+    <row r="3" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="32" t="str">
+        <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
+        <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="J3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="52" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="J3" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="44" t="str">
-        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
-        <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
-      </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
       <c r="J4" s="12" t="s">
         <v>98</v>
       </c>
@@ -2654,15 +2950,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
+    <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
       <c r="J5" s="12" t="s">
         <v>129</v>
       </c>
@@ -2670,236 +2968,230 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="J6" s="15" t="s">
+    <row r="6" spans="1:11" ht="20.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J6" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="16" t="str">
+      <c r="K6" s="15" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="70" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="72"/>
+      <c r="G7" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="G7" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="H7" s="18" t="str">
+      <c r="H7" s="73" t="str">
         <f>K7</f>
         <v>RV/NEK/BOC/202607/014</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="19" t="str">
+      <c r="K7" s="18" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",H9=""),"","RV/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(H9,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>RV/NEK/BOC/202607/014</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="H8" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="J8" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="J8" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="K8" s="21" t="str">
+      <c r="K8" s="19" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="G9" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="H9" s="22">
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G9" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H9" s="75">
         <v>46228</v>
       </c>
       <c r="J9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K9" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>MYR</v>
       </c>
     </row>
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="39" t="str">
+      <c r="A11" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="63" t="str">
         <f>$K$9</f>
         <v>MYR</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="39" t="s">
+      <c r="F11" s="62"/>
+      <c r="G11" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" s="67"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="60" t="s">
         <v>140</v>
       </c>
-      <c r="H11" s="40"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="33" t="s">
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="58">
+        <v>2793</v>
+      </c>
+      <c r="F12" s="57"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="68"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="60"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="68"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="60"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="68"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="60"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="68"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="60"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="68"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="60"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="68"/>
+    </row>
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="35">
-        <v>2793</v>
-      </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="31"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="33"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="31"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="33"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="31"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="33"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="31"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="33"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="31"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="33"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="31"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="43">
+      <c r="B18" s="65"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="66">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
-      <c r="F18" s="31"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="31"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="69"/>
+    </row>
+    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
+      <c r="B20" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="72"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B23" s="38"/>
+      <c r="C23" s="29"/>
+      <c r="E23" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="31"/>
-      <c r="E23" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="31"/>
+        <v>145</v>
+      </c>
+      <c r="B25" s="38"/>
+      <c r="C25" s="29"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="29"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="31"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G12:H12"/>
+  <mergeCells count="37">
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="E17:F17"/>
@@ -2916,20 +3208,32 @@
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>"BOC,BOCOM,MBB,OCBC,TBC,UOB"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8" xr:uid="{7B3847F5-DF2D-4DCE-9E94-D0E2696626CE}">
+      <formula1>"IBG,Cheque,TT"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -2969,65 +3273,66 @@
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="J1" s="10" t="s">
         <v>126</v>
       </c>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="J2" s="42" t="s">
+    <row r="2" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="32" t="str">
+        <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
+        <v>Co. Reg. No. 198401003022 (115540-H)</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="J2" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="31"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="44" t="str">
+      <c r="K2" s="29"/>
+    </row>
+    <row r="3" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="32" t="str">
+        <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
+        <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="J3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="52" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="J3" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="44" t="str">
-        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
-        <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
-      </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
       <c r="J4" s="12" t="s">
         <v>98</v>
       </c>
@@ -3035,15 +3340,17 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
+    <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
       <c r="J5" s="12" t="s">
         <v>129</v>
       </c>
@@ -3051,66 +3358,66 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="J6" s="15" t="s">
+    <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.35">
+      <c r="J6" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="16" t="str">
+      <c r="K6" s="15" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Malayan Banking Berhad (Maybank)</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="G7" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="H7" s="18" t="str">
+      <c r="H7" s="17" t="str">
         <f>K7</f>
         <v>INV/NEK/MBB/202607/014</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="19" t="str">
+      <c r="K7" s="18" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",H8=""),"","INV/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(H8,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>INV/NEK/MBB/202607/014</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="G8" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="H8" s="22">
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="G8" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8" s="20">
         <v>46204</v>
       </c>
-      <c r="J8" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="K8" s="21" t="str">
+      <c r="J8" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="K8" s="19" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
+      <c r="A9" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
       <c r="J9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K9" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
@@ -3118,176 +3425,157 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="36"/>
+      <c r="C11" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="39" t="str">
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="35" t="str">
         <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
         <v>AMOUNT (MYR)</v>
       </c>
-      <c r="H11" s="40"/>
+      <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="36">
+      <c r="A12" s="34">
         <v>1</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="33" t="s">
+      <c r="B12" s="29"/>
+      <c r="C12" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="33">
+        <v>9000</v>
+      </c>
+      <c r="H12" s="29"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="34"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="29"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="34"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="29"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="34"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="29"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="34"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="29"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="34"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="29"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="35">
-        <v>9000</v>
-      </c>
-      <c r="H12" s="31"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="36"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="31"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="36"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="31"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="36"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="31"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="36"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="31"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="36"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="31"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="43">
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="30">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
-      <c r="H18" s="31"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
+      <c r="B20" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
+      <c r="A22" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="46" t="str">
+      <c r="A23" s="43" t="str">
         <f>IF($K$3="","","Bank : "&amp;IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),""))</f>
         <v>Bank : Malayan Banking Berhad (Maybank)</v>
       </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
+      <c r="A25" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A18:F18"/>
+  <mergeCells count="35">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="G17:H17"/>
@@ -3303,6 +3591,26 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0500-000001000000}">
@@ -3310,7 +3618,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -3350,65 +3658,66 @@
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="J1" s="10" t="s">
         <v>126</v>
       </c>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="J2" s="42" t="s">
+    <row r="2" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="32" t="str">
+        <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
+        <v>Co. Reg. No. 198401003022 (115540-H)</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="J2" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="31"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="44" t="str">
+      <c r="K2" s="29"/>
+    </row>
+    <row r="3" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="32" t="str">
+        <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
+        <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="J3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="52" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="J3" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="44" t="str">
-        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
-        <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
-      </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
       <c r="J4" s="12" t="s">
         <v>98</v>
       </c>
@@ -3416,15 +3725,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
+    <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
       <c r="J5" s="12" t="s">
         <v>129</v>
       </c>
@@ -3432,66 +3743,66 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="J6" s="15" t="s">
+    <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.35">
+      <c r="J6" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="16" t="str">
+      <c r="K6" s="15" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="G7" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="H7" s="18" t="str">
+      <c r="H7" s="17" t="str">
         <f>K7</f>
         <v>OR/NEK/BOC/202607/014</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="19" t="str">
+      <c r="K7" s="18" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",H8=""),"","OR/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(H8,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>OR/NEK/BOC/202607/014</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="G8" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="H8" s="22">
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="G8" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8" s="20">
         <v>46204</v>
       </c>
-      <c r="J8" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="K8" s="21" t="str">
+      <c r="J8" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="K8" s="19" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="47" t="s">
-        <v>155</v>
-      </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
+      <c r="A9" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
       <c r="J9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K9" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
@@ -3499,178 +3810,199 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="36"/>
+      <c r="C11" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="39" t="str">
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="35" t="str">
         <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
         <v>AMOUNT (MYR)</v>
       </c>
-      <c r="H11" s="40"/>
+      <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="36">
+      <c r="A12" s="34">
         <v>1</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="33" t="s">
+      <c r="B12" s="29"/>
+      <c r="C12" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="33">
+        <v>9000</v>
+      </c>
+      <c r="H12" s="29"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="34"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="29"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="34"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="29"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="34"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="29"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="34"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="29"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="34"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="29"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="35">
-        <v>9000</v>
-      </c>
-      <c r="H12" s="31"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="36"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="31"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="36"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="31"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="36"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="31"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="36"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="31"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="36"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="31"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="43">
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="30">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
-      <c r="H18" s="31"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
+      <c r="B20" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="45" t="s">
         <v>165</v>
       </c>
-      <c r="C22" s="48" t="s">
-        <v>166</v>
-      </c>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C23" s="49" t="str">
+        <v>166</v>
+      </c>
+      <c r="C23" s="46" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" s="45" t="s">
         <v>168</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="50" t="s">
-        <v>170</v>
-      </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
+      <c r="A28" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="37">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="A28:H28"/>
@@ -3687,26 +4019,6 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0600-000001000000}">
@@ -3714,7 +4026,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -3754,61 +4066,63 @@
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
       <c r="J1" s="10" t="s">
         <v>126</v>
       </c>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="J2" s="42" t="s">
+    <row r="2" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="32" t="str">
+        <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
+        <v>Co. Reg. No. 198401003022 (115540-H)</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="J2" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="31"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="44" t="str">
+      <c r="K2" s="29"/>
+    </row>
+    <row r="3" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="32" t="str">
+        <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
+        <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
+      </c>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="J3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="52" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="J3" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="44" t="str">
-        <f>IF($K$3="","",IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      ")&amp;"Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)))</f>
-        <v>Co. Reg. No. 198401003022 (115540-H)      Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
-      </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="54"/>
       <c r="J4" s="12" t="s">
         <v>98</v>
       </c>
@@ -3816,14 +4130,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+    <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="55" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
       <c r="J5" s="12" t="s">
         <v>129</v>
       </c>
@@ -3831,292 +4148,300 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="J6" s="15" t="s">
+    <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.35">
+      <c r="J6" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="16" t="str">
+      <c r="K6" s="15" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="C7" s="29"/>
+      <c r="E7" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="F7" s="48" t="s">
-        <v>175</v>
-      </c>
-      <c r="G7" s="31"/>
-      <c r="J7" s="15" t="s">
+      <c r="G7" s="29"/>
+      <c r="J7" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="19" t="str">
+      <c r="K7" s="18" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",$K$9=""),"","SAL/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT($K$9,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>SAL/NEK/BOC/202607/014</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="45" t="s">
         <v>176</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="C8" s="29"/>
+      <c r="E8" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="E8" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="J8" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="K8" s="21" t="str">
+      <c r="G8" s="29"/>
+      <c r="J8" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="K8" s="19" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="E9" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="F9" s="51" t="str">
+        <v>178</v>
+      </c>
+      <c r="F9" s="48" t="str">
         <f>K7</f>
         <v>SAL/NEK/BOC/202607/014</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="29"/>
       <c r="J9" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="K9" s="21">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="47" t="s">
         <v>180</v>
       </c>
-      <c r="K9" s="23">
-        <v>46228</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="52" t="s">
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="E10" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="E10" s="52" t="s">
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="24" t="s">
+      <c r="B11" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="23">
+        <v>6500</v>
+      </c>
+      <c r="E11" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="F11" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="25">
-        <v>6500</v>
-      </c>
-      <c r="E11" s="24" t="s">
+      <c r="G11" s="23">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="B12" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="25">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="24" t="s">
+      <c r="C12" s="23">
+        <v>300</v>
+      </c>
+      <c r="E12" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="F12" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="25">
-        <v>300</v>
-      </c>
-      <c r="E12" s="24" t="s">
+      <c r="G12" s="23">
+        <v>104.15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E13" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F13" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="25">
-        <v>104.15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="E13" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="25">
+      <c r="G13" s="23">
         <v>11.9</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="24">
         <f>C11+C12</f>
         <v>6800</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="24">
         <f>SUM(G11:G13)</f>
         <v>932.05</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="24" t="s">
+      <c r="B17" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="23">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B18" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="25">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="24" t="s">
+      <c r="C18" s="23">
+        <v>29.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B19" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="25">
-        <v>29.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="24" t="s">
+      <c r="C19" s="23">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B20" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="25">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="24" t="s">
+      <c r="C20" s="23">
+        <v>44.65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B21" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="25">
-        <v>44.65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="25">
+      <c r="C21" s="23">
         <v>295.5</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="24">
         <f>SUM(C17:C21)</f>
         <v>1129.8</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="52" t="s">
-        <v>197</v>
-      </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
+      <c r="A24" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="24" t="s">
-        <v>188</v>
+      <c r="A25" s="22" t="s">
+        <v>187</v>
       </c>
       <c r="B25" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="25">
         <f>C14</f>
         <v>6800</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="24" t="s">
-        <v>198</v>
+      <c r="A26" s="22" t="s">
+        <v>197</v>
       </c>
       <c r="B26" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="25">
         <f>C22</f>
         <v>1129.8</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="B27" s="28" t="s">
+      <c r="A27" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="B27" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="27">
         <f>C25-C26</f>
         <v>5670.2</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
+      <c r="A29" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="A24:C24"/>
@@ -4125,13 +4450,6 @@
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="E10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0700-000001000000}">
@@ -4139,7 +4457,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">

--- a/templates/NEK_Document_Templates.xlsx
+++ b/templates/NEK_Document_Templates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB8F017-6792-42FD-BF48-4C6E537ECBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF629C1-FA64-47BE-A063-F7056CC08E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="210">
   <si>
     <t>NEK GROUP — DOCUMENT HOUSE STYLE</t>
   </si>
@@ -482,18 +482,12 @@
     <t>PREPARED BY</t>
   </si>
   <si>
-    <t>RECEIVED BY</t>
-  </si>
-  <si>
     <t>ISSUED BY</t>
   </si>
   <si>
     <t>APPROVED BY</t>
   </si>
   <si>
-    <t>Internal control document. Retain the signed copy for audit.</t>
-  </si>
-  <si>
     <t>RECEIVING VOUCHER</t>
   </si>
   <si>
@@ -681,6 +675,9 @@
   </si>
   <si>
     <t>Mode of Payment :</t>
+  </si>
+  <si>
+    <t>Signature :</t>
   </si>
 </sst>
 </file>
@@ -691,7 +688,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -823,8 +820,27 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -846,8 +862,14 @@
         <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -876,15 +898,6 @@
       <top/>
       <bottom style="medium">
         <color rgb="FF808080"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1116,11 +1129,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1173,38 +1234,85 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1212,84 +1320,58 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1825,18 +1907,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" t="s">
         <v>201</v>
-      </c>
-      <c r="B2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C2" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1844,10 +1926,10 @@
         <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1855,10 +1937,10 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1866,10 +1948,10 @@
         <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2489,51 +2571,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="str">
+      <c r="A1" s="40" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
       <c r="J1" s="10" t="s">
         <v>126</v>
       </c>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32" t="str">
+    <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="71" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="J2" s="28" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="J2" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="29"/>
-    </row>
-    <row r="3" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="32" t="str">
+      <c r="K2" s="32"/>
+    </row>
+    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="71" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
       <c r="J3" s="12" t="s">
         <v>52</v>
       </c>
@@ -2541,18 +2623,18 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="52" t="str">
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="71" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
       <c r="J4" s="12" t="s">
         <v>98</v>
       </c>
@@ -2561,16 +2643,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="52" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
       <c r="J5" s="12" t="s">
         <v>129</v>
       </c>
@@ -2591,16 +2673,16 @@
       <c r="A7" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="70" t="s">
+      <c r="B7" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="72"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="43"/>
       <c r="G7" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="H7" s="73" t="str">
+      <c r="H7" s="28" t="str">
         <f>K7</f>
         <v>PV/NEK/BOC/202607/014</v>
       </c>
@@ -2614,9 +2696,9 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="G8" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="H8" s="74" t="s">
+        <v>208</v>
+      </c>
+      <c r="H8" s="29" t="s">
         <v>135</v>
       </c>
       <c r="J8" s="14" t="s">
@@ -2631,11 +2713,11 @@
       <c r="G9" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="H9" s="75">
+      <c r="H9" s="30">
         <v>46228</v>
       </c>
       <c r="J9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K9" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
@@ -2644,180 +2726,166 @@
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="63" t="str">
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="50" t="str">
         <f>$K$9</f>
         <v>MYR</v>
       </c>
-      <c r="F11" s="62"/>
-      <c r="G11" s="63" t="s">
+      <c r="F11" s="46"/>
+      <c r="G11" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="67"/>
+      <c r="H11" s="51"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="60" t="s">
+      <c r="A12" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="58">
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="37">
         <v>2793</v>
       </c>
-      <c r="F12" s="57"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="68"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="39"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="60"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="68"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="39"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="60"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="68"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="39"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="60"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="68"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="39"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="60"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="68"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="39"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="60"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="68"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="39"/>
     </row>
     <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="65"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="66">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="49">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="69"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="47"/>
     </row>
     <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="4" t="str">
+      <c r="A20" s="72" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="76" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="72"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="12" t="s">
+      <c r="B20" s="75"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="74"/>
+    </row>
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="77" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="29"/>
-      <c r="E23" s="12" t="s">
+      <c r="B23" s="78"/>
+      <c r="C23" s="79"/>
+      <c r="E23" s="80" t="s">
+        <v>209</v>
+      </c>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+    </row>
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="77" t="s">
         <v>144</v>
       </c>
-      <c r="F23" s="38"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="12" t="s">
+      <c r="B25" s="78"/>
+      <c r="C25" s="79"/>
+      <c r="E25" s="82" t="s">
+        <v>209</v>
+      </c>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+    </row>
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="77" t="s">
         <v>145</v>
       </c>
-      <c r="B25" s="38"/>
-      <c r="C25" s="29"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B27" s="38"/>
-      <c r="C27" s="29"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="79"/>
+      <c r="E27" s="82" t="s">
+        <v>209</v>
+      </c>
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="83"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A17:D17"/>
+  <mergeCells count="40">
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="A14:D14"/>
@@ -2833,6 +2901,31 @@
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F27:H27"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -2879,51 +2972,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="str">
+      <c r="A1" s="40" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
       <c r="J1" s="10" t="s">
         <v>126</v>
       </c>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32" t="str">
+    <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="71" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="J2" s="28" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="J2" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="29"/>
-    </row>
-    <row r="3" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="32" t="str">
+      <c r="K2" s="32"/>
+    </row>
+    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="71" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
       <c r="J3" s="12" t="s">
         <v>52</v>
       </c>
@@ -2931,18 +3024,18 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="52" t="str">
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="71" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
       <c r="J4" s="12" t="s">
         <v>98</v>
       </c>
@@ -2951,16 +3044,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="50" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
+      <c r="A5" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
       <c r="J5" s="12" t="s">
         <v>129</v>
       </c>
@@ -2979,18 +3072,18 @@
     </row>
     <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="70" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="72"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="43"/>
       <c r="G7" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="H7" s="73" t="str">
+        <v>148</v>
+      </c>
+      <c r="H7" s="28" t="str">
         <f>K7</f>
         <v>RV/NEK/BOC/202607/014</v>
       </c>
@@ -3004,9 +3097,9 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="G8" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="H8" s="74" t="s">
+        <v>208</v>
+      </c>
+      <c r="H8" s="29" t="s">
         <v>135</v>
       </c>
       <c r="J8" s="14" t="s">
@@ -3021,11 +3114,11 @@
       <c r="G9" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="H9" s="75">
+      <c r="H9" s="30">
         <v>46228</v>
       </c>
       <c r="J9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K9" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
@@ -3034,180 +3127,166 @@
     </row>
     <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="63" t="str">
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="50" t="str">
         <f>$K$9</f>
         <v>MYR</v>
       </c>
-      <c r="F11" s="62"/>
-      <c r="G11" s="63" t="s">
+      <c r="F11" s="46"/>
+      <c r="G11" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="67"/>
+      <c r="H11" s="51"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="60" t="s">
+      <c r="A12" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="58">
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="37">
         <v>2793</v>
       </c>
-      <c r="F12" s="57"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="68"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="39"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="60"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="68"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="39"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="60"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="68"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="39"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="60"/>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="68"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="39"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="60"/>
-      <c r="B16" s="57"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="68"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="39"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="60"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="68"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="39"/>
     </row>
     <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="65"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="66">
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="49">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="69"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="47"/>
     </row>
     <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="4" t="str">
+      <c r="A20" s="72" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="76" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="72"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="12" t="s">
+      <c r="B20" s="75"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="74"/>
+    </row>
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="77" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="29"/>
-      <c r="E23" s="12" t="s">
+      <c r="B23" s="78"/>
+      <c r="C23" s="79"/>
+      <c r="E23" s="80" t="s">
+        <v>209</v>
+      </c>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+    </row>
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="77" t="s">
         <v>144</v>
       </c>
-      <c r="F23" s="38"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="12" t="s">
+      <c r="B25" s="78"/>
+      <c r="C25" s="79"/>
+      <c r="E25" s="82" t="s">
+        <v>209</v>
+      </c>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+    </row>
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="77" t="s">
         <v>145</v>
       </c>
-      <c r="B25" s="38"/>
-      <c r="C25" s="29"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B27" s="38"/>
-      <c r="C27" s="29"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="79"/>
+      <c r="E27" s="82" t="s">
+        <v>209</v>
+      </c>
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="83"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A17:D17"/>
+  <mergeCells count="40">
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="A14:D14"/>
@@ -3223,6 +3302,31 @@
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F27:H27"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0400-000001000000}">
@@ -3269,51 +3373,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="str">
+      <c r="A1" s="40" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
       <c r="J1" s="10" t="s">
         <v>126</v>
       </c>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32" t="str">
+    <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="71" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="J2" s="28" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="J2" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="29"/>
-    </row>
-    <row r="3" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="32" t="str">
+      <c r="K2" s="32"/>
+    </row>
+    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="71" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
       <c r="J3" s="12" t="s">
         <v>52</v>
       </c>
@@ -3321,18 +3425,18 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="52" t="str">
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="71" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
       <c r="J4" s="12" t="s">
         <v>98</v>
       </c>
@@ -3341,16 +3445,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="50" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
+      <c r="A5" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
       <c r="J5" s="12" t="s">
         <v>129</v>
       </c>
@@ -3369,10 +3473,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H7" s="17" t="str">
         <f>K7</f>
@@ -3387,13 +3491,13 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="56" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
       <c r="G8" s="16" t="s">
         <v>137</v>
       </c>
@@ -3409,15 +3513,15 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="42" t="s">
-        <v>154</v>
-      </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
+      <c r="A9" s="63" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
       <c r="J9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K9" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
@@ -3425,157 +3529,176 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="35" t="str">
+      <c r="A11" s="58" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="59"/>
+      <c r="C11" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="58" t="str">
         <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
         <v>AMOUNT (MYR)</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="H11" s="59"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="34">
+      <c r="A12" s="57">
         <v>1</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="33">
+      <c r="B12" s="32"/>
+      <c r="C12" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="55">
         <v>9000</v>
       </c>
-      <c r="H12" s="29"/>
+      <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="34"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="29"/>
+      <c r="A13" s="57"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="32"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="34"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="29"/>
+      <c r="A14" s="57"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="32"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="34"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="29"/>
+      <c r="A15" s="57"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="32"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="34"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="29"/>
+      <c r="A16" s="57"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="32"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="34"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="29"/>
+      <c r="A17" s="57"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="32"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="41" t="s">
-        <v>158</v>
-      </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="30">
+      <c r="A18" s="62" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="60">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
-      <c r="H18" s="29"/>
+      <c r="H18" s="32"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="43" t="s">
-        <v>159</v>
-      </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
+      <c r="A22" s="61" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="43" t="str">
+      <c r="A23" s="61" t="str">
         <f>IF($K$3="","","Bank : "&amp;IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),""))</f>
         <v>Bank : Malayan Banking Berhad (Maybank)</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
+      <c r="A25" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="G17:H17"/>
@@ -3592,25 +3715,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0500-000001000000}">
@@ -3654,51 +3758,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="str">
+      <c r="A1" s="40" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
       <c r="J1" s="10" t="s">
         <v>126</v>
       </c>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32" t="str">
+    <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="71" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="J2" s="28" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="J2" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="29"/>
-    </row>
-    <row r="3" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="32" t="str">
+      <c r="K2" s="32"/>
+    </row>
+    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="71" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
       <c r="J3" s="12" t="s">
         <v>52</v>
       </c>
@@ -3706,18 +3810,18 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="52" t="str">
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="71" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
       <c r="J4" s="12" t="s">
         <v>98</v>
       </c>
@@ -3726,16 +3830,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
+      <c r="A5" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
       <c r="J5" s="12" t="s">
         <v>129</v>
       </c>
@@ -3754,10 +3858,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H7" s="17" t="str">
         <f>K7</f>
@@ -3772,13 +3876,13 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="56" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
       <c r="G8" s="16" t="s">
         <v>137</v>
       </c>
@@ -3794,15 +3898,15 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="42" t="s">
-        <v>154</v>
-      </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
+      <c r="A9" s="63" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
       <c r="J9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K9" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
@@ -3810,178 +3914,199 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="35" t="str">
+      <c r="A11" s="58" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="59"/>
+      <c r="C11" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="58" t="str">
         <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
         <v>AMOUNT (MYR)</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="H11" s="59"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="34">
+      <c r="A12" s="57">
         <v>1</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="33">
+      <c r="B12" s="32"/>
+      <c r="C12" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="55">
         <v>9000</v>
       </c>
-      <c r="H12" s="29"/>
+      <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="34"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="29"/>
+      <c r="A13" s="57"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="32"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="34"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="29"/>
+      <c r="A14" s="57"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="32"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="34"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="29"/>
+      <c r="A15" s="57"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="32"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="34"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="29"/>
+      <c r="A16" s="57"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="32"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="34"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="29"/>
+      <c r="A17" s="57"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="32"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="41" t="s">
-        <v>158</v>
-      </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="30">
+      <c r="A18" s="62" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="60">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
-      <c r="H18" s="29"/>
+      <c r="H18" s="32"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C22" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
+        <v>162</v>
+      </c>
+      <c r="C22" s="64" t="s">
+        <v>163</v>
+      </c>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C23" s="46" t="str">
+        <v>164</v>
+      </c>
+      <c r="C23" s="65" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="64" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="C24" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
+      <c r="A28" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B20:H20"/>
@@ -3998,27 +4123,6 @@
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="A4:H4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0600-000001000000}">
@@ -4062,48 +4166,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="str">
+      <c r="A1" s="40" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
       <c r="J1" s="10" t="s">
         <v>126</v>
       </c>
       <c r="K1" s="11"/>
     </row>
-    <row r="2" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32" t="str">
+    <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="71" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="J2" s="28" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="J2" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="29"/>
-    </row>
-    <row r="3" spans="1:11" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="32" t="str">
+      <c r="K2" s="32"/>
+    </row>
+    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="71" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
       <c r="J3" s="12" t="s">
         <v>52</v>
       </c>
@@ -4111,18 +4215,17 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="52" t="str">
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="71" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="54"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
       <c r="J4" s="12" t="s">
         <v>98</v>
       </c>
@@ -4131,16 +4234,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="55" t="s">
-        <v>170</v>
-      </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
+      <c r="A5" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
       <c r="J5" s="12" t="s">
         <v>129</v>
       </c>
@@ -4159,19 +4262,19 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="64" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="32"/>
+      <c r="E7" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="F7" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="E7" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F7" s="45" t="s">
-        <v>174</v>
-      </c>
-      <c r="G7" s="29"/>
+      <c r="G7" s="32"/>
       <c r="J7" s="14" t="s">
         <v>134</v>
       </c>
@@ -4182,19 +4285,19 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="64" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="32"/>
+      <c r="E8" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B8" s="45" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="29"/>
-      <c r="E8" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="29"/>
+      <c r="G8" s="32"/>
       <c r="J8" s="14" t="s">
         <v>136</v>
       </c>
@@ -4205,35 +4308,35 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="E9" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F9" s="48" t="str">
+        <v>176</v>
+      </c>
+      <c r="F9" s="67" t="str">
         <f>K7</f>
         <v>SAL/NEK/BOC/202607/014</v>
       </c>
-      <c r="G9" s="29"/>
+      <c r="G9" s="32"/>
       <c r="J9" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K9" s="21">
         <v>46228</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="E10" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
+      <c r="A10" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="E10" s="70" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>63</v>
@@ -4242,7 +4345,7 @@
         <v>6500</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>63</v>
@@ -4253,7 +4356,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>63</v>
@@ -4262,7 +4365,7 @@
         <v>300</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>63</v>
@@ -4273,7 +4376,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="E13" s="22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>63</v>
@@ -4284,7 +4387,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>63</v>
@@ -4294,7 +4397,7 @@
         <v>6800</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>63</v>
@@ -4305,15 +4408,15 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="47" t="s">
-        <v>189</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
+      <c r="A16" s="70" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>63</v>
@@ -4324,7 +4427,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B18" s="22" t="s">
         <v>63</v>
@@ -4335,7 +4438,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>63</v>
@@ -4346,7 +4449,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B20" s="22" t="s">
         <v>63</v>
@@ -4357,7 +4460,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B21" s="22" t="s">
         <v>63</v>
@@ -4368,7 +4471,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>63</v>
@@ -4379,15 +4482,15 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="47" t="s">
-        <v>196</v>
-      </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
+      <c r="A24" s="70" t="s">
+        <v>194</v>
+      </c>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B25" t="s">
         <v>63</v>
@@ -4399,7 +4502,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s">
         <v>63</v>
@@ -4411,7 +4514,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="26" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B27" s="26" t="s">
         <v>63</v>
@@ -4422,18 +4525,26 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
+      <c r="A29" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="E10:G10"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="F9:G9"/>
@@ -4442,14 +4553,6 @@
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="E10:G10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0700-000001000000}">

--- a/templates/NEK_Document_Templates.xlsx
+++ b/templates/NEK_Document_Templates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF629C1-FA64-47BE-A063-F7056CC08E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21AD657-4AAE-4F25-ACE9-952580B1F8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -479,9 +479,6 @@
     <t>[amount in words]</t>
   </si>
   <si>
-    <t>PREPARED BY</t>
-  </si>
-  <si>
     <t>ISSUED BY</t>
   </si>
   <si>
@@ -678,6 +675,9 @@
   </si>
   <si>
     <t>Signature :</t>
+  </si>
+  <si>
+    <t>CHECKED BY</t>
   </si>
 </sst>
 </file>
@@ -688,7 +688,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -751,58 +751,9 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF1F3864"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8"/>
-      <color rgb="FF808080"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -827,20 +778,102 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
       <sz val="10"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -868,8 +901,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1046,21 +1085,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1081,51 +1105,6 @@
       </top>
       <bottom style="medium">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1177,11 +1156,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1200,178 +1201,194 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="20" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="20" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="20" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="26" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1907,18 +1924,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" t="s">
         <v>199</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>200</v>
-      </c>
-      <c r="C2" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1926,10 +1943,10 @@
         <v>90</v>
       </c>
       <c r="B3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" t="s">
         <v>202</v>
-      </c>
-      <c r="C3" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1937,10 +1954,10 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" t="s">
         <v>204</v>
-      </c>
-      <c r="C4" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1948,10 +1965,10 @@
         <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2570,322 +2587,523 @@
     <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="str">
+    <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="J1" s="10" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="11"/>
-    </row>
-    <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="71" t="str">
+      <c r="K1" s="15"/>
+    </row>
+    <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="16" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="J2" s="48" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="32"/>
-    </row>
-    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="71" t="str">
+      <c r="K2" s="18"/>
+    </row>
+    <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="16" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="J3" s="12" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="71" t="str">
+    <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="16" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="J4" s="12" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="19" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="52" t="s">
+    <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="J5" s="12" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="19">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="20.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J6" s="14" t="s">
+    <row r="6" spans="1:11" ht="26.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="15" t="str">
+      <c r="K6" s="23" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:11" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="43"/>
-      <c r="G7" s="16" t="s">
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="H7" s="28" t="str">
+      <c r="G7" s="83" t="str">
         <f>K7</f>
         <v>PV/NEK/BOC/202607/014</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="H7" s="82"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="18" t="str">
-        <f>IF(OR($K$3="",$K$4="",$K$5="",H9=""),"","PV/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(H9,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
+      <c r="K7" s="26" t="str">
+        <f>IF(OR($K$3="",$K$4="",$K$5="",G9=""),"","PV/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(G9,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>PV/NEK/BOC/202607/014</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="G8" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="H8" s="29" t="s">
+    <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="81" t="s">
+        <v>207</v>
+      </c>
+      <c r="G8" s="85" t="s">
         <v>135</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="H8" s="84"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="K8" s="19" t="str">
+      <c r="K8" s="27" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G9" s="16" t="s">
+    <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="81" t="s">
         <v>137</v>
       </c>
-      <c r="H9" s="30">
+      <c r="G9" s="87">
         <v>46228</v>
       </c>
-      <c r="J9" t="s">
-        <v>207</v>
-      </c>
-      <c r="K9" t="str">
+      <c r="H9" s="86"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="K9" s="13" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>MYR</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="45" t="s">
+    <row r="10" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+    </row>
+    <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="50" t="str">
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="30" t="str">
         <f>$K$9</f>
         <v>MYR</v>
       </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="50" t="s">
+      <c r="F11" s="29"/>
+      <c r="G11" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="51"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="33" t="s">
+      <c r="H11" s="31"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+    </row>
+    <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="37">
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="34">
         <v>2793</v>
       </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="39"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="33"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="39"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="33"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="33"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="33"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="33"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
-    </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="35" t="s">
+      <c r="F12" s="33"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+    </row>
+    <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="32"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+    </row>
+    <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="32"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+    </row>
+    <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="32"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+    </row>
+    <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="32"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+    </row>
+    <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="32"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+    </row>
+    <row r="18" spans="1:11" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="49">
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="39">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="47"/>
-    </row>
-    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="72" t="str">
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+    </row>
+    <row r="19" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="88" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="75"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="74"/>
-    </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="77" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+    </row>
+    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+    </row>
+    <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="78"/>
-      <c r="C23" s="79"/>
-      <c r="E23" s="80" t="s">
+      <c r="B23" s="45"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+    </row>
+    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+    </row>
+    <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-    </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="77" t="s">
+      <c r="B25" s="45"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+    </row>
+    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+    </row>
+    <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="B25" s="78"/>
-      <c r="C25" s="79"/>
-      <c r="E25" s="82" t="s">
-        <v>209</v>
-      </c>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-    </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="77" t="s">
-        <v>145</v>
-      </c>
-      <c r="B27" s="78"/>
-      <c r="C27" s="79"/>
-      <c r="E27" s="82" t="s">
-        <v>209</v>
-      </c>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="31"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+    </row>
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+    </row>
+    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+    </row>
+    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A30" s="51"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="43">
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B7:D7"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="A14:D14"/>
@@ -2901,37 +3119,13 @@
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="G7:H7"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"BOC,BOCOM,MBB,OCBC,TBC,UOB"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8" xr:uid="{FD09BFF1-BCFD-453E-903F-2DC48E0C55F9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8" xr:uid="{FD09BFF1-BCFD-453E-903F-2DC48E0C55F9}">
       <formula1>"IBG,Cheque,TT"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2971,322 +3165,523 @@
     <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="str">
+    <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="J1" s="10" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="11"/>
-    </row>
-    <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="71" t="str">
+      <c r="K1" s="15"/>
+    </row>
+    <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="16" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="J2" s="48" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="32"/>
-    </row>
-    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="71" t="str">
+      <c r="K2" s="18"/>
+    </row>
+    <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="16" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="J3" s="12" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="71" t="str">
+    <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="16" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="J4" s="12" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="19" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="52" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="J5" s="12" t="s">
+    <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="19">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="20.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J6" s="14" t="s">
+    <row r="6" spans="1:11" ht="26.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="15" t="str">
+      <c r="K6" s="23" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:11" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="78" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="81" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="44" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="43"/>
-      <c r="G7" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="H7" s="28" t="str">
+      <c r="G7" s="83" t="str">
         <f>K7</f>
         <v>RV/NEK/BOC/202607/014</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="H7" s="82"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="18" t="str">
-        <f>IF(OR($K$3="",$K$4="",$K$5="",H9=""),"","RV/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(H9,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
+      <c r="K7" s="26" t="str">
+        <f>IF(OR($K$3="",$K$4="",$K$5="",G9=""),"","RV/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(G9,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>RV/NEK/BOC/202607/014</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="G8" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="H8" s="29" t="s">
+    <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="81" t="s">
+        <v>207</v>
+      </c>
+      <c r="G8" s="85" t="s">
         <v>135</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="H8" s="84"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="K8" s="19" t="str">
+      <c r="K8" s="27" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G9" s="16" t="s">
+    <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="81" t="s">
         <v>137</v>
       </c>
-      <c r="H9" s="30">
+      <c r="G9" s="87">
         <v>46228</v>
       </c>
-      <c r="J9" t="s">
-        <v>207</v>
-      </c>
-      <c r="K9" t="str">
+      <c r="H9" s="86"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="K9" s="13" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>MYR</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="45" t="s">
+    <row r="10" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+    </row>
+    <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="50" t="str">
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="30" t="str">
         <f>$K$9</f>
         <v>MYR</v>
       </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="50" t="s">
+      <c r="F11" s="29"/>
+      <c r="G11" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="51"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="33" t="s">
+      <c r="H11" s="31"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+    </row>
+    <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="37">
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="34">
         <v>2793</v>
       </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="39"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="33"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="39"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="33"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="33"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="39"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="33"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="33"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
-    </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="35" t="s">
+      <c r="F12" s="33"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+    </row>
+    <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="32"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+    </row>
+    <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="32"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+    </row>
+    <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="32"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+    </row>
+    <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="32"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+    </row>
+    <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="32"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+    </row>
+    <row r="18" spans="1:11" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="49">
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="39">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="47"/>
-    </row>
-    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="72" t="str">
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+    </row>
+    <row r="19" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="88" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="75"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="74"/>
-    </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="77" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+    </row>
+    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+    </row>
+    <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="78"/>
-      <c r="C23" s="79"/>
-      <c r="E23" s="80" t="s">
+      <c r="B23" s="45"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+    </row>
+    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+    </row>
+    <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-    </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="77" t="s">
+      <c r="B25" s="45"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+    </row>
+    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+    </row>
+    <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="B25" s="78"/>
-      <c r="C25" s="79"/>
-      <c r="E25" s="82" t="s">
-        <v>209</v>
-      </c>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-    </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="77" t="s">
-        <v>145</v>
-      </c>
-      <c r="B27" s="78"/>
-      <c r="C27" s="79"/>
-      <c r="E27" s="82" t="s">
-        <v>209</v>
-      </c>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="31"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+    </row>
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+    </row>
+    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+    </row>
+    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A30" s="51"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="43">
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B7:D7"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="A14:D14"/>
@@ -3302,37 +3697,13 @@
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="G7:H7"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>"BOC,BOCOM,MBB,OCBC,TBC,UOB"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8" xr:uid="{7B3847F5-DF2D-4DCE-9E94-D0E2696626CE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8" xr:uid="{7B3847F5-DF2D-4DCE-9E94-D0E2696626CE}">
       <formula1>"IBG,Cheque,TT"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3358,7 +3729,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -3372,333 +3743,493 @@
     <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="str">
+    <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="J1" s="10" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="11"/>
-    </row>
-    <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="71" t="str">
+      <c r="K1" s="15"/>
+    </row>
+    <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="16" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="J2" s="48" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="32"/>
-    </row>
-    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="71" t="str">
+      <c r="K2" s="18"/>
+    </row>
+    <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="16" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="J3" s="12" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="71" t="str">
+    <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="16" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="J4" s="12" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="19" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="52" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="J5" s="12" t="s">
+    <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="19">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.35">
-      <c r="J6" s="14" t="s">
+    <row r="6" spans="1:11" ht="26" x14ac:dyDescent="0.4">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="15" t="str">
+      <c r="K6" s="23" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Malayan Banking Berhad (Maybank)</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="H7" s="17" t="str">
+      <c r="H7" s="52" t="str">
         <f>K7</f>
         <v>INV/NEK/MBB/202607/014</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="I7" s="13"/>
+      <c r="J7" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="18" t="str">
+      <c r="K7" s="26" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",H8=""),"","INV/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(H8,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>INV/NEK/MBB/202607/014</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="56" t="s">
+    <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="G8" s="16" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="54">
         <v>46204</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="I8" s="13"/>
+      <c r="J8" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="K8" s="19" t="str">
+      <c r="K8" s="27" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="63" t="s">
-        <v>152</v>
-      </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="J9" t="s">
-        <v>207</v>
-      </c>
-      <c r="K9" t="str">
+    <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="K9" s="13" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>MYR</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="58" t="s">
+    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+    </row>
+    <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="56" t="s">
+        <v>152</v>
+      </c>
+      <c r="B11" s="57"/>
+      <c r="C11" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="58" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="58" t="str">
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="56" t="str">
         <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
         <v>AMOUNT (MYR)</v>
       </c>
-      <c r="H11" s="59"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="57">
+      <c r="H11" s="57"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+    </row>
+    <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="58">
         <v>1</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="56" t="s">
+      <c r="B12" s="18"/>
+      <c r="C12" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="59">
+        <v>9000</v>
+      </c>
+      <c r="H12" s="18"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+    </row>
+    <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="58"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+    </row>
+    <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="58"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+    </row>
+    <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="58"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+    </row>
+    <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="58"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+    </row>
+    <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="58"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+    </row>
+    <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="55">
-        <v>9000</v>
-      </c>
-      <c r="H12" s="32"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="57"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="32"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="57"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="32"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="57"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="32"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="57"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="32"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="57"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="32"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="62" t="s">
-        <v>156</v>
-      </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="60">
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="61">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
-      <c r="H18" s="32"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="str">
+      <c r="H18" s="18"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+    </row>
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="24" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="61" t="s">
-        <v>157</v>
-      </c>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="61" t="str">
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+    </row>
+    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A22" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+    </row>
+    <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="63" t="str">
         <f>IF($K$3="","","Bank : "&amp;IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),""))</f>
         <v>Bank : Malayan Banking Berhad (Maybank)</v>
       </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+    </row>
+    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+    </row>
+    <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+    </row>
+    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+    </row>
+    <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+    </row>
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+    </row>
+    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+    </row>
+    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="G17:H17"/>
@@ -3715,6 +4246,25 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0500-000001000000}">
@@ -3743,7 +4293,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -3757,335 +4307,524 @@
     <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="str">
+    <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="J1" s="10" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="11"/>
-    </row>
-    <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="71" t="str">
+      <c r="K1" s="15"/>
+    </row>
+    <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="16" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="J2" s="48" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="32"/>
-    </row>
-    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="71" t="str">
+      <c r="K2" s="18"/>
+    </row>
+    <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="16" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="J3" s="12" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="71" t="str">
+    <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="16" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="J4" s="12" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="19" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="52" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="J5" s="12" t="s">
+    <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="19">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.35">
-      <c r="J6" s="14" t="s">
+    <row r="6" spans="1:11" ht="26" x14ac:dyDescent="0.4">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="15" t="str">
+      <c r="K6" s="23" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="H7" s="17" t="str">
+      <c r="H7" s="52" t="str">
         <f>K7</f>
         <v>OR/NEK/BOC/202607/014</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="I7" s="13"/>
+      <c r="J7" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="18" t="str">
+      <c r="K7" s="26" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",H8=""),"","OR/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(H8,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>OR/NEK/BOC/202607/014</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="56" t="s">
+    <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="G8" s="16" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="54">
         <v>46204</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="I8" s="13"/>
+      <c r="J8" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="K8" s="19" t="str">
+      <c r="K8" s="27" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="63" t="s">
-        <v>152</v>
-      </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="J9" t="s">
-        <v>207</v>
-      </c>
-      <c r="K9" t="str">
+    <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="K9" s="13" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>MYR</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="58" t="s">
+    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+    </row>
+    <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="56" t="s">
+        <v>152</v>
+      </c>
+      <c r="B11" s="57"/>
+      <c r="C11" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="58" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="58" t="str">
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="56" t="str">
         <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
         <v>AMOUNT (MYR)</v>
       </c>
-      <c r="H11" s="59"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="57">
+      <c r="H11" s="57"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+    </row>
+    <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="58">
         <v>1</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="56" t="s">
+      <c r="B12" s="18"/>
+      <c r="C12" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="59">
+        <v>9000</v>
+      </c>
+      <c r="H12" s="18"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+    </row>
+    <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="58"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+    </row>
+    <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="58"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+    </row>
+    <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="58"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+    </row>
+    <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="58"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+    </row>
+    <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="58"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+    </row>
+    <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="55">
-        <v>9000</v>
-      </c>
-      <c r="H12" s="32"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="57"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="32"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="57"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="32"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="57"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="32"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="57"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="32"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="57"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="32"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="62" t="s">
-        <v>156</v>
-      </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="60">
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="61">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
-      <c r="H18" s="32"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="str">
+      <c r="H18" s="18"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+    </row>
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="24" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+    </row>
+    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A22" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="64" t="s">
         <v>162</v>
       </c>
-      <c r="C22" s="64" t="s">
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+    </row>
+    <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>164</v>
-      </c>
+      <c r="B23" s="13"/>
       <c r="C23" s="65" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+    </row>
+    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A24" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C24" s="64" t="s">
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+    </row>
+    <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+    </row>
+    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A26" s="66" t="s">
         <v>166</v>
       </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="66" t="s">
-        <v>167</v>
-      </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+    </row>
+    <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+    </row>
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A28" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+    </row>
+    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+    </row>
+    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="A28:H28"/>
@@ -4102,27 +4841,6 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0600-000001000000}">
@@ -4151,7 +4869,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -4165,378 +4883,588 @@
     <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="str">
+    <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="J1" s="10" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="11"/>
-    </row>
-    <row r="2" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="71" t="str">
+      <c r="K1" s="15"/>
+    </row>
+    <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="16" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="J2" s="48" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="32"/>
-    </row>
-    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="71" t="str">
+      <c r="K2" s="18"/>
+    </row>
+    <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="16" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="J3" s="12" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="71" t="str">
+    <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="16" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="J4" s="12" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="19" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="J5" s="12" t="s">
+    <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="19">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="20" x14ac:dyDescent="0.35">
-      <c r="J6" s="14" t="s">
+    <row r="6" spans="1:11" ht="26" x14ac:dyDescent="0.4">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="15" t="str">
+      <c r="K6" s="23" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="64" t="s">
+      <c r="C7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="F7" s="64" t="s">
-        <v>172</v>
-      </c>
-      <c r="G7" s="32"/>
-      <c r="J7" s="14" t="s">
+      <c r="G7" s="18"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="18" t="str">
+      <c r="K7" s="26" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",$K$9=""),"","SAL/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT($K$9,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>SAL/NEK/BOC/202607/014</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="64" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="64" t="s">
+      <c r="C8" s="18"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="C8" s="32"/>
-      <c r="E8" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F8" s="57" t="s">
+      <c r="F8" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="J8" s="14" t="s">
+      <c r="G8" s="18"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="K8" s="19" t="str">
+      <c r="K8" s="27" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="E9" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="F9" s="67" t="str">
+    <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F9" s="69" t="str">
         <f>K7</f>
         <v>SAL/NEK/BOC/202607/014</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="J9" s="12" t="s">
+      <c r="G9" s="18"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="K9" s="70">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A10" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="K9" s="21">
-        <v>46228</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="70" t="s">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="71" t="s">
         <v>178</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="E10" s="70" t="s">
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+    </row>
+    <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="72" t="s">
         <v>179</v>
       </c>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="22" t="s">
+      <c r="B11" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="73">
+        <v>6500</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="72" t="s">
         <v>180</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="F11" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="23">
-        <v>6500</v>
-      </c>
-      <c r="E11" s="22" t="s">
+      <c r="G11" s="73">
+        <v>816</v>
+      </c>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+    </row>
+    <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="72" t="s">
         <v>181</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="B12" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="23">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="22" t="s">
+      <c r="C12" s="73">
+        <v>300</v>
+      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="72" t="s">
         <v>182</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="F12" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="23">
-        <v>300</v>
-      </c>
-      <c r="E12" s="22" t="s">
+      <c r="G12" s="73">
+        <v>104.15</v>
+      </c>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+    </row>
+    <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="72" t="s">
         <v>183</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F13" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="23">
-        <v>104.15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="E13" s="22" t="s">
+      <c r="G13" s="73">
+        <v>11.9</v>
+      </c>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+    </row>
+    <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="B14" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="23">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="24">
+      <c r="C14" s="74">
         <f>C11+C12</f>
         <v>6800</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="D14" s="13"/>
+      <c r="E14" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="74">
         <f>SUM(G11:G13)</f>
         <v>932.05</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="70" t="s">
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+    </row>
+    <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+    </row>
+    <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="71" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+    </row>
+    <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="72" t="s">
         <v>187</v>
       </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="22" t="s">
+      <c r="B17" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="73">
+        <v>748</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+    </row>
+    <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="72" t="s">
         <v>188</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B18" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="23">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="22" t="s">
+      <c r="C18" s="73">
+        <v>29.75</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+    </row>
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A19" s="72" t="s">
         <v>189</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B19" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="23">
-        <v>29.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="22" t="s">
+      <c r="C19" s="73">
+        <v>11.9</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="72" t="s">
         <v>190</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B20" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="23">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="22" t="s">
+      <c r="C20" s="73">
+        <v>44.65</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A21" s="72" t="s">
         <v>191</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B21" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="23">
-        <v>44.65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="22" t="s">
+      <c r="C21" s="73">
+        <v>295.5</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+    </row>
+    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A22" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B22" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C21" s="23">
-        <v>295.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="24">
+      <c r="C22" s="74">
         <f>SUM(C17:C21)</f>
         <v>1129.8</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="70" t="s">
-        <v>194</v>
-      </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+    </row>
+    <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+    </row>
+    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A24" s="71" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+    </row>
+    <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="72" t="s">
+        <v>184</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="75">
         <f>C14</f>
         <v>6800</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+    </row>
+    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A26" s="72" t="s">
+        <v>194</v>
+      </c>
+      <c r="B26" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="75">
         <f>C22</f>
         <v>1129.8</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="B27" s="26" t="s">
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+    </row>
+    <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="76" t="s">
+        <v>195</v>
+      </c>
+      <c r="B27" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="77">
         <f>C25-C26</f>
         <v>5670.2</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+    </row>
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+    </row>
+    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A29" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+    </row>
+    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.4">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="A24:C24"/>
@@ -4545,14 +5473,6 @@
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="E10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0700-000001000000}">

--- a/templates/NEK_Document_Templates.xlsx
+++ b/templates/NEK_Document_Templates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21AD657-4AAE-4F25-ACE9-952580B1F8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE7BEDB-A0FE-4A3A-91FB-CF2C815CD6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,8 +26,8 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Invoice!$A$1:$H$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Official Receipt'!$A$1:$H$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Payment Voucher'!$A$1:$H$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Receiving Voucher'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Payment Voucher'!$A$1:$H$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Receiving Voucher'!$A$1:$H$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Salary Slip'!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -688,7 +688,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -761,13 +761,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -846,19 +839,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -869,6 +849,66 @@
       <b/>
       <sz val="13"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1182,7 +1222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1202,192 +1242,198 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="23" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="20" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="27" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="29" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="20" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="20" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="26" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2587,523 +2633,496 @@
     <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="str">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="58" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="14" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="15"/>
-    </row>
-    <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="16" t="str">
+      <c r="K1" s="13"/>
+    </row>
+    <row r="2" spans="1:11" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="59" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="17" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="18"/>
-    </row>
-    <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="16" t="str">
+      <c r="K2" s="31"/>
+    </row>
+    <row r="3" spans="1:11" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="59" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="13"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="16" t="str">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="59" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="14" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:11" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="13"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="14">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="26.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="22" t="s">
+    <row r="6" spans="1:11" ht="4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="23" t="str">
+      <c r="K6" s="16" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:11" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="62" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="81" t="s">
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="63" t="s">
         <v>133</v>
       </c>
-      <c r="G7" s="83" t="str">
+      <c r="G7" s="64" t="str">
         <f>K7</f>
         <v>PV/NEK/BOC/202607/014</v>
       </c>
-      <c r="H7" s="82"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="22" t="s">
+      <c r="H7" s="65"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="26" t="str">
+      <c r="K7" s="19" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",G9=""),"","PV/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(G9,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>PV/NEK/BOC/202607/014</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="81" t="s">
+    <row r="8" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="63" t="s">
         <v>207</v>
       </c>
-      <c r="G8" s="85" t="s">
+      <c r="G8" s="66" t="s">
         <v>135</v>
       </c>
-      <c r="H8" s="84"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="22" t="s">
+      <c r="H8" s="67"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K8" s="27" t="str">
+      <c r="K8" s="20" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="81" t="s">
+    <row r="9" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="87">
+      <c r="G9" s="68">
         <v>46228</v>
       </c>
-      <c r="H9" s="86"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13" t="s">
+      <c r="H9" s="69"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="K9" s="13" t="str">
+      <c r="K9" s="11" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>MYR</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-    </row>
-    <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="28" t="s">
+    <row r="10" spans="1:11" ht="4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+    </row>
+    <row r="11" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="70" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="30" t="str">
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="71" t="str">
         <f>$K$9</f>
         <v>MYR</v>
       </c>
-      <c r="F11" s="29"/>
-      <c r="G11" s="30" t="s">
+      <c r="F11" s="72"/>
+      <c r="G11" s="71" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="31"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-    </row>
-    <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="32" t="s">
+      <c r="H11" s="73"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+    </row>
+    <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="74" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="34">
+      <c r="B12" s="75"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="76">
         <v>2793</v>
       </c>
-      <c r="F12" s="33"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-    </row>
-    <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="32"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-    </row>
-    <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="32"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-    </row>
-    <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="32"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-    </row>
-    <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="32"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-    </row>
-    <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="32"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-    </row>
-    <row r="18" spans="1:11" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="37" t="s">
+      <c r="F12" s="75"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+    </row>
+    <row r="13" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="74"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+    </row>
+    <row r="14" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="74"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+    </row>
+    <row r="15" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="74"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="78"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="74"/>
+      <c r="B16" s="75"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+    </row>
+    <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="74"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+    </row>
+    <row r="18" spans="1:11" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="79" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="39">
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="80">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-    </row>
-    <row r="19" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-    </row>
-    <row r="20" spans="1:11" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="88" t="str">
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+    </row>
+    <row r="19" spans="1:11" ht="4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+    </row>
+    <row r="20" spans="1:11" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="83" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-    </row>
-    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-    </row>
-    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-    </row>
-    <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="44" t="s">
+      <c r="B20" s="84"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+    </row>
+    <row r="21" spans="1:11" ht="4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+    </row>
+    <row r="22" spans="1:11" ht="4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+    </row>
+    <row r="23" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="88" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="47" t="s">
+      <c r="B23" s="89"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="91" t="s">
         <v>208</v>
       </c>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-    </row>
-    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-    </row>
-    <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="44" t="s">
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+    </row>
+    <row r="24" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+    </row>
+    <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="88" t="s">
         <v>209</v>
       </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="49" t="s">
+      <c r="B25" s="89"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="63" t="s">
         <v>208</v>
       </c>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-    </row>
-    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-    </row>
-    <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="44" t="s">
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+    </row>
+    <row r="26" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+    </row>
+    <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="49" t="s">
+      <c r="B27" s="89"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="63" t="s">
         <v>208</v>
       </c>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-    </row>
-    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-    </row>
-    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-    </row>
-    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A30" s="51"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+    </row>
+    <row r="28" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+    </row>
+    <row r="29" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+    </row>
+    <row r="30" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="30"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="B7:D7"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="A14:D14"/>
@@ -3120,6 +3139,33 @@
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F27:H27"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -3129,8 +3175,9 @@
       <formula1>"IBG,Cheque,TT"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
+  <pageSetup paperSize="11" scale="97" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -3165,523 +3212,496 @@
     <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="str">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="58" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="14" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="15"/>
-    </row>
-    <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="16" t="str">
+      <c r="K1" s="13"/>
+    </row>
+    <row r="2" spans="1:11" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="59" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="17" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="18"/>
-    </row>
-    <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="16" t="str">
+      <c r="K2" s="31"/>
+    </row>
+    <row r="3" spans="1:11" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="59" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="13"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="16" t="str">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="59" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="14" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:11" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="13"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="14">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="26.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="22" t="s">
+    <row r="6" spans="1:11" ht="4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="23" t="str">
+      <c r="K6" s="16" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:11" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="62" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="81" t="s">
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="63" t="s">
         <v>147</v>
       </c>
-      <c r="G7" s="83" t="str">
+      <c r="G7" s="64" t="str">
         <f>K7</f>
         <v>RV/NEK/BOC/202607/014</v>
       </c>
-      <c r="H7" s="82"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="22" t="s">
+      <c r="H7" s="65"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="26" t="str">
+      <c r="K7" s="19" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",G9=""),"","RV/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(G9,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>RV/NEK/BOC/202607/014</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="81" t="s">
+    <row r="8" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="63" t="s">
         <v>207</v>
       </c>
-      <c r="G8" s="85" t="s">
+      <c r="G8" s="66" t="s">
         <v>135</v>
       </c>
-      <c r="H8" s="84"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="22" t="s">
+      <c r="H8" s="67"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K8" s="27" t="str">
+      <c r="K8" s="20" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="81" t="s">
+    <row r="9" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="87">
+      <c r="G9" s="68">
         <v>46228</v>
       </c>
-      <c r="H9" s="86"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13" t="s">
+      <c r="H9" s="69"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="K9" s="13" t="str">
+      <c r="K9" s="11" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>MYR</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-    </row>
-    <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="28" t="s">
+    <row r="10" spans="1:11" ht="4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+    </row>
+    <row r="11" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="70" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="30" t="str">
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="71" t="str">
         <f>$K$9</f>
         <v>MYR</v>
       </c>
-      <c r="F11" s="29"/>
-      <c r="G11" s="30" t="s">
+      <c r="F11" s="72"/>
+      <c r="G11" s="71" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="31"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-    </row>
-    <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="32" t="s">
+      <c r="H11" s="73"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+    </row>
+    <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="74" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="34">
+      <c r="B12" s="75"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="76">
         <v>2793</v>
       </c>
-      <c r="F12" s="33"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-    </row>
-    <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="32"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-    </row>
-    <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="32"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-    </row>
-    <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="32"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-    </row>
-    <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="32"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-    </row>
-    <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="32"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-    </row>
-    <row r="18" spans="1:11" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="37" t="s">
+      <c r="F12" s="75"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+    </row>
+    <row r="13" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="74"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+    </row>
+    <row r="14" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="74"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+    </row>
+    <row r="15" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="74"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="78"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="74"/>
+      <c r="B16" s="75"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+    </row>
+    <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="74"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+    </row>
+    <row r="18" spans="1:11" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="79" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="39">
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="80">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-    </row>
-    <row r="19" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-    </row>
-    <row r="20" spans="1:11" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="88" t="str">
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+    </row>
+    <row r="19" spans="1:11" ht="4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+    </row>
+    <row r="20" spans="1:11" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="83" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-    </row>
-    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-    </row>
-    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-    </row>
-    <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="44" t="s">
+      <c r="B20" s="84"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+    </row>
+    <row r="21" spans="1:11" ht="4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+    </row>
+    <row r="22" spans="1:11" ht="4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+    </row>
+    <row r="23" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="88" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="47" t="s">
+      <c r="B23" s="89"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="91" t="s">
         <v>208</v>
       </c>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-    </row>
-    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-    </row>
-    <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="44" t="s">
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+    </row>
+    <row r="24" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+    </row>
+    <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="88" t="s">
         <v>209</v>
       </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="49" t="s">
+      <c r="B25" s="89"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="63" t="s">
         <v>208</v>
       </c>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-    </row>
-    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-    </row>
-    <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="44" t="s">
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+    </row>
+    <row r="26" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+    </row>
+    <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="49" t="s">
+      <c r="B27" s="89"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="63" t="s">
         <v>208</v>
       </c>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-    </row>
-    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-    </row>
-    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-    </row>
-    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A30" s="51"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+    </row>
+    <row r="28" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+    </row>
+    <row r="29" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+    </row>
+    <row r="30" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="30"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="B7:D7"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="A14:D14"/>
@@ -3698,6 +3718,33 @@
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F27:H27"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0400-000001000000}">
@@ -3707,8 +3754,9 @@
       <formula1>"IBG,Cheque,TT"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
+  <pageSetup paperSize="11" scale="97" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -3744,492 +3792,511 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="str">
+      <c r="A1" s="33" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="14" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="15"/>
+      <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="16" t="str">
+      <c r="A2" s="38" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="17" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="18"/>
+      <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="16" t="str">
+      <c r="A3" s="38" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="13"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="14" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="16" t="str">
+      <c r="A4" s="38" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="14" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="13"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="14">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="26" x14ac:dyDescent="0.4">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="22" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="23" t="str">
+      <c r="K6" s="16" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Malayan Banking Berhad (Maybank)</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="25" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="H7" s="52" t="str">
+      <c r="H7" s="21" t="str">
         <f>K7</f>
         <v>INV/NEK/MBB/202607/014</v>
       </c>
-      <c r="I7" s="13"/>
-      <c r="J7" s="22" t="s">
+      <c r="I7" s="11"/>
+      <c r="J7" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="26" t="str">
+      <c r="K7" s="19" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",H8=""),"","INV/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(H8,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>INV/NEK/MBB/202607/014</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="25" t="s">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="H8" s="54">
+      <c r="H8" s="22">
         <v>46204</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="22" t="s">
+      <c r="I8" s="11"/>
+      <c r="J8" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K8" s="27" t="str">
+      <c r="K8" s="20" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="K9" s="13" t="str">
+      <c r="K9" s="11" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>MYR</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="56" t="s">
+      <c r="B11" s="46"/>
+      <c r="C11" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="56" t="str">
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="45" t="str">
         <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
         <v>AMOUNT (MYR)</v>
       </c>
-      <c r="H11" s="57"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="58">
+      <c r="A12" s="44">
         <v>1</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="53" t="s">
+      <c r="B12" s="31"/>
+      <c r="C12" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="59">
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="42">
         <v>9000</v>
       </c>
-      <c r="H12" s="18"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="58"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="58"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
+      <c r="A14" s="44"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="58"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
+      <c r="A15" s="44"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="58"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="58"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
+      <c r="A17" s="44"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="60" t="s">
+      <c r="A18" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="61">
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="47">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
     </row>
     <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
     </row>
     <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24" t="str">
+      <c r="A20" s="17" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
     </row>
     <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
     </row>
     <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="63" t="str">
+      <c r="A23" s="48" t="str">
         <f>IF($K$3="","","Bank : "&amp;IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),""))</f>
         <v>Bank : Malayan Banking Berhad (Maybank)</v>
       </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
     </row>
     <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
     </row>
     <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
     </row>
     <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
     </row>
     <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
     </row>
     <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
     </row>
     <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="G17:H17"/>
@@ -4246,33 +4313,15 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>"BOC,BOCOM,MBB,OCBC,TBC,UOB"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
+  <pageSetup paperSize="11" scale="67" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -4308,502 +4357,523 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="str">
+      <c r="A1" s="33" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="14" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="15"/>
+      <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="16" t="str">
+      <c r="A2" s="38" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="17" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="18"/>
+      <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="16" t="str">
+      <c r="A3" s="38" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="13"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="14" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="16" t="str">
+      <c r="A4" s="38" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="14" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="13"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="14">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="26" x14ac:dyDescent="0.4">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="22" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="23" t="str">
+      <c r="K6" s="16" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="25" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="H7" s="52" t="str">
+      <c r="H7" s="21" t="str">
         <f>K7</f>
         <v>OR/NEK/BOC/202607/014</v>
       </c>
-      <c r="I7" s="13"/>
-      <c r="J7" s="22" t="s">
+      <c r="I7" s="11"/>
+      <c r="J7" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="26" t="str">
+      <c r="K7" s="19" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",H8=""),"","OR/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT(H8,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>OR/NEK/BOC/202607/014</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="25" t="s">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="H8" s="54">
+      <c r="H8" s="22">
         <v>46204</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="22" t="s">
+      <c r="I8" s="11"/>
+      <c r="J8" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K8" s="27" t="str">
+      <c r="K8" s="20" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="K9" s="13" t="str">
+      <c r="K9" s="11" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>MYR</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="56" t="s">
+      <c r="B11" s="46"/>
+      <c r="C11" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="56" t="str">
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="45" t="str">
         <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
         <v>AMOUNT (MYR)</v>
       </c>
-      <c r="H11" s="57"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="58">
+      <c r="A12" s="44">
         <v>1</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="53" t="s">
+      <c r="B12" s="31"/>
+      <c r="C12" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="59">
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="42">
         <v>9000</v>
       </c>
-      <c r="H12" s="18"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="58"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="58"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
+      <c r="A14" s="44"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="58"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
+      <c r="A15" s="44"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="58"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="58"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
+      <c r="A17" s="44"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="60" t="s">
+      <c r="A18" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="61">
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="47">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
     </row>
     <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
     </row>
     <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24" t="str">
+      <c r="A20" s="17" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
     </row>
     <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
     </row>
     <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="64" t="s">
+      <c r="B22" s="11"/>
+      <c r="C22" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="65" t="str">
+      <c r="B23" s="11"/>
+      <c r="C23" s="52" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
     </row>
     <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="64" t="s">
+      <c r="B24" s="11"/>
+      <c r="C24" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
     </row>
     <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A26" s="66" t="s">
+      <c r="A26" s="53" t="s">
         <v>166</v>
       </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
     </row>
     <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
     </row>
     <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A28" s="51" t="s">
+      <c r="A28" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
     </row>
     <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
     </row>
     <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B20:H20"/>
@@ -4820,35 +4890,15 @@
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="A4:H4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0600-000001000000}">
       <formula1>"BOC,BOCOM,MBB,OCBC,TBC,UOB"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
+  <pageSetup paperSize="11" scale="59" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -4884,579 +4934,587 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="str">
+      <c r="A1" s="33" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="14" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="K1" s="15"/>
+      <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="16" t="str">
+      <c r="A2" s="38" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="17" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="18"/>
+      <c r="K2" s="31"/>
     </row>
     <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="16" t="str">
+      <c r="A3" s="38" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="14" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="16" t="str">
+      <c r="A4" s="38" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="14" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="55" t="s">
         <v>167</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="13"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="14">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="26" x14ac:dyDescent="0.4">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="22" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K6" s="23" t="str">
+      <c r="K6" s="16" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="24" t="s">
+      <c r="C7" s="31"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="F7" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="22" t="s">
+      <c r="G7" s="31"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="K7" s="26" t="str">
+      <c r="K7" s="19" t="str">
         <f>IF(OR($K$3="",$K$4="",$K$5="",$K$9=""),"","SAL/"&amp;$K$3&amp;"/"&amp;$K$4&amp;"/"&amp;TEXT($K$9,"yyyymm")&amp;"/"&amp;TEXT($K$5,"000"))</f>
         <v>SAL/NEK/BOC/202607/014</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="24" t="s">
+      <c r="C8" s="31"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="22" t="s">
+      <c r="G8" s="31"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K8" s="27" t="str">
+      <c r="K8" s="20" t="str">
         <f>IF(OR($K$3="",$K$4=""),"",IF(ISNUMBER(MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"","! bank code not linked to this entity"))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
       <c r="E9" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="F9" s="69" t="str">
+      <c r="F9" s="54" t="str">
         <f>K7</f>
         <v>SAL/NEK/BOC/202607/014</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
       <c r="J9" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="K9" s="70">
+      <c r="K9" s="23">
         <v>46228</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A10" s="71" t="s">
+      <c r="A10" s="57" t="s">
         <v>177</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="71" t="s">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="57" t="s">
         <v>178</v>
       </c>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="72" t="s">
+      <c r="A11" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="73">
+      <c r="C11" s="25">
         <v>6500</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="72" t="s">
+      <c r="D11" s="11"/>
+      <c r="E11" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="73">
+      <c r="G11" s="25">
         <v>816</v>
       </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="72" t="s">
+      <c r="A12" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="72" t="s">
+      <c r="B12" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="73">
+      <c r="C12" s="25">
         <v>300</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="72" t="s">
+      <c r="D12" s="11"/>
+      <c r="E12" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="F12" s="72" t="s">
+      <c r="F12" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="73">
+      <c r="G12" s="25">
         <v>104.15</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="72" t="s">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="72" t="s">
+      <c r="F13" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="73">
+      <c r="G13" s="25">
         <v>11.9</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="74">
+      <c r="C14" s="26">
         <f>C11+C12</f>
         <v>6800</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="24" t="s">
+      <c r="D14" s="11"/>
+      <c r="E14" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="74">
+      <c r="G14" s="26">
         <f>SUM(G11:G13)</f>
         <v>932.05</v>
       </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="71" t="s">
+      <c r="A16" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="72" t="s">
+      <c r="A17" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="B17" s="72" t="s">
+      <c r="B17" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="73">
+      <c r="C17" s="25">
         <v>748</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="72" t="s">
+      <c r="A18" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="B18" s="72" t="s">
+      <c r="B18" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="73">
+      <c r="C18" s="25">
         <v>29.75</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
     </row>
     <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="73">
+      <c r="C19" s="25">
         <v>11.9</v>
       </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
     </row>
     <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="72" t="s">
+      <c r="A20" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="B20" s="72" t="s">
+      <c r="B20" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="73">
+      <c r="C20" s="25">
         <v>44.65</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
     </row>
     <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A21" s="72" t="s">
+      <c r="A21" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="B21" s="72" t="s">
+      <c r="B21" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C21" s="73">
+      <c r="C21" s="25">
         <v>295.5</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
     </row>
     <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="74">
+      <c r="C22" s="26">
         <f>SUM(C17:C21)</f>
         <v>1129.8</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
     </row>
     <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A24" s="71" t="s">
+      <c r="A24" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="72" t="s">
+      <c r="A25" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="75">
+      <c r="C25" s="27">
         <f>C14</f>
         <v>6800</v>
       </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
     </row>
     <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A26" s="72" t="s">
+      <c r="A26" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="75">
+      <c r="C26" s="27">
         <f>C22</f>
         <v>1129.8</v>
       </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
     </row>
     <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="76" t="s">
+      <c r="A27" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="77">
+      <c r="C27" s="29">
         <f>C25-C26</f>
         <v>5670.2</v>
       </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
     </row>
     <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
     </row>
     <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
     </row>
     <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="E10:G10"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="F9:G9"/>
@@ -5465,22 +5523,15 @@
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="E10:G10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0700-000001000000}">
       <formula1>"BOC,BOCOM,MBB,OCBC,TBC,UOB"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
+  <pageSetup paperSize="11" scale="58" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">

--- a/templates/NEK_Document_Templates.xlsx
+++ b/templates/NEK_Document_Templates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE7BEDB-A0FE-4A3A-91FB-CF2C815CD6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C840434-6C31-4BAB-BBED-CF05EB567690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -948,7 +948,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1149,19 +1149,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1197,32 +1184,23 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1277,66 +1255,122 @@
     <xf numFmtId="43" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="23" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="29" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="27" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1346,93 +1380,41 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="27" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="29" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2622,7 +2604,7 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="1" max="1" width="16.6328125" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
@@ -2634,17 +2616,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="58" t="str">
+      <c r="A1" s="50" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
       <c r="I1" s="11"/>
       <c r="J1" s="12" t="s">
         <v>126</v>
@@ -2652,35 +2634,35 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="10" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="59" t="str">
+      <c r="A2" s="40" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="31"/>
+      <c r="K2" s="35"/>
     </row>
     <row r="3" spans="1:11" ht="10" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="59" t="str">
+      <c r="A3" s="40" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
@@ -2690,17 +2672,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="59" t="str">
+      <c r="A4" s="40" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
@@ -2710,16 +2692,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
@@ -2747,23 +2729,23 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="87" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="63" t="s">
+      <c r="C7" s="56"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="86" t="s">
         <v>133</v>
       </c>
-      <c r="G7" s="64" t="str">
+      <c r="G7" s="89" t="str">
         <f>K7</f>
         <v>PV/NEK/BOC/202607/014</v>
       </c>
-      <c r="H7" s="65"/>
+      <c r="H7" s="90"/>
       <c r="I7" s="11"/>
       <c r="J7" s="15" t="s">
         <v>134</v>
@@ -2779,13 +2761,13 @@
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
-      <c r="F8" s="63" t="s">
+      <c r="F8" s="86" t="s">
         <v>207</v>
       </c>
-      <c r="G8" s="66" t="s">
+      <c r="G8" s="91" t="s">
         <v>135</v>
       </c>
-      <c r="H8" s="67"/>
+      <c r="H8" s="92"/>
       <c r="I8" s="11"/>
       <c r="J8" s="15" t="s">
         <v>136</v>
@@ -2801,13 +2783,13 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
-      <c r="F9" s="63" t="s">
+      <c r="F9" s="86" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="68">
+      <c r="G9" s="57">
         <v>46228</v>
       </c>
-      <c r="H9" s="69"/>
+      <c r="H9" s="93"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11" t="s">
         <v>206</v>
@@ -2831,121 +2813,121 @@
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="70" t="s">
+      <c r="A11" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="71" t="str">
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="45" t="str">
         <f>$K$9</f>
         <v>MYR</v>
       </c>
-      <c r="F11" s="72"/>
-      <c r="G11" s="71" t="s">
+      <c r="F11" s="46"/>
+      <c r="G11" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="73"/>
+      <c r="H11" s="47"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="75"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="76">
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="42">
         <v>2793</v>
       </c>
-      <c r="F12" s="75"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="78"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="74"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="78"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="74"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="78"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="74"/>
-      <c r="B15" s="75"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="78"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="74"/>
-      <c r="B16" s="75"/>
-      <c r="C16" s="75"/>
-      <c r="D16" s="75"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="75"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="78"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="44"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="74"/>
-      <c r="B17" s="75"/>
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="75"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="78"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="79" t="s">
+      <c r="A18" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="80">
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="36">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="82"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="55"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -2964,17 +2946,17 @@
       <c r="K19" s="11"/>
     </row>
     <row r="20" spans="1:11" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="83" t="str">
+      <c r="A20" s="81" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="84"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="87"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="84"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -3006,18 +2988,18 @@
       <c r="K22" s="11"/>
     </row>
     <row r="23" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="88" t="s">
+      <c r="A23" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="89"/>
-      <c r="C23" s="90"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="52"/>
       <c r="D23" s="11"/>
-      <c r="E23" s="91" t="s">
+      <c r="E23" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -3036,18 +3018,18 @@
       <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="88" t="s">
+      <c r="A25" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="B25" s="89"/>
-      <c r="C25" s="90"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="52"/>
       <c r="D25" s="11"/>
-      <c r="E25" s="63" t="s">
+      <c r="E25" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -3066,18 +3048,18 @@
       <c r="K26" s="11"/>
     </row>
     <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="89"/>
-      <c r="C27" s="90"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="63" t="s">
+      <c r="E27" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
@@ -3109,20 +3091,46 @@
       <c r="K29" s="11"/>
     </row>
     <row r="30" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="30"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
+      <c r="A30" s="58"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="42">
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G8:H8"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="A14:D14"/>
@@ -3139,33 +3147,6 @@
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F27:H27"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -3175,9 +3156,9 @@
       <formula1>"IBG,Cheque,TT"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
-  <pageSetup paperSize="11" scale="97" orientation="landscape" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.3" bottom="0.3" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -3201,7 +3182,7 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="1" max="1" width="16.6328125" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
@@ -3213,17 +3194,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="58" t="str">
+      <c r="A1" s="50" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
       <c r="I1" s="11"/>
       <c r="J1" s="12" t="s">
         <v>126</v>
@@ -3231,35 +3212,35 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="10" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="59" t="str">
+      <c r="A2" s="40" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="31"/>
+      <c r="K2" s="35"/>
     </row>
     <row r="3" spans="1:11" ht="10" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="59" t="str">
+      <c r="A3" s="40" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
@@ -3269,17 +3250,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="59" t="str">
+      <c r="A4" s="40" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
@@ -3289,16 +3270,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
@@ -3326,23 +3307,23 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="87" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="63" t="s">
+      <c r="C7" s="56"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="86" t="s">
         <v>147</v>
       </c>
-      <c r="G7" s="64" t="str">
+      <c r="G7" s="89" t="str">
         <f>K7</f>
         <v>RV/NEK/BOC/202607/014</v>
       </c>
-      <c r="H7" s="65"/>
+      <c r="H7" s="90"/>
       <c r="I7" s="11"/>
       <c r="J7" s="15" t="s">
         <v>134</v>
@@ -3358,13 +3339,13 @@
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
-      <c r="F8" s="63" t="s">
+      <c r="F8" s="86" t="s">
         <v>207</v>
       </c>
-      <c r="G8" s="66" t="s">
+      <c r="G8" s="91" t="s">
         <v>135</v>
       </c>
-      <c r="H8" s="67"/>
+      <c r="H8" s="92"/>
       <c r="I8" s="11"/>
       <c r="J8" s="15" t="s">
         <v>136</v>
@@ -3380,13 +3361,13 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
-      <c r="F9" s="63" t="s">
+      <c r="F9" s="86" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="68">
+      <c r="G9" s="57">
         <v>46228</v>
       </c>
-      <c r="H9" s="69"/>
+      <c r="H9" s="93"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11" t="s">
         <v>206</v>
@@ -3410,121 +3391,121 @@
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="70" t="s">
+      <c r="A11" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="71" t="str">
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="45" t="str">
         <f>$K$9</f>
         <v>MYR</v>
       </c>
-      <c r="F11" s="72"/>
-      <c r="G11" s="71" t="s">
+      <c r="F11" s="46"/>
+      <c r="G11" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="73"/>
+      <c r="H11" s="47"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="75"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="76">
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="42">
         <v>2793</v>
       </c>
-      <c r="F12" s="75"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="78"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="74"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="78"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="74"/>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="78"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="74"/>
-      <c r="B15" s="75"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="78"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="44"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="74"/>
-      <c r="B16" s="75"/>
-      <c r="C16" s="75"/>
-      <c r="D16" s="75"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="75"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="78"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="44"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="74"/>
-      <c r="B17" s="75"/>
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="75"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="78"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="44"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="79" t="s">
+      <c r="A18" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="80">
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="36">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="82"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="55"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -3543,17 +3524,17 @@
       <c r="K19" s="11"/>
     </row>
     <row r="20" spans="1:11" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="83" t="str">
+      <c r="A20" s="81" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="84"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="87"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="84"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -3585,18 +3566,18 @@
       <c r="K22" s="11"/>
     </row>
     <row r="23" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="88" t="s">
+      <c r="A23" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="89"/>
-      <c r="C23" s="90"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="52"/>
       <c r="D23" s="11"/>
-      <c r="E23" s="91" t="s">
+      <c r="E23" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -3615,18 +3596,18 @@
       <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="88" t="s">
+      <c r="A25" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="B25" s="89"/>
-      <c r="C25" s="90"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="52"/>
       <c r="D25" s="11"/>
-      <c r="E25" s="63" t="s">
+      <c r="E25" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -3645,18 +3626,18 @@
       <c r="K26" s="11"/>
     </row>
     <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="89"/>
-      <c r="C27" s="90"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="63" t="s">
+      <c r="E27" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
@@ -3688,20 +3669,46 @@
       <c r="K29" s="11"/>
     </row>
     <row r="30" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="30"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
+      <c r="A30" s="58"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="42">
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G8:H8"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="A14:D14"/>
@@ -3718,33 +3725,6 @@
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F27:H27"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0400-000001000000}">
@@ -3754,9 +3734,9 @@
       <formula1>"IBG,Cheque,TT"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
-  <pageSetup paperSize="11" scale="97" orientation="landscape" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.3" bottom="0.3" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -3792,17 +3772,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="33" t="str">
+      <c r="A1" s="70" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
       <c r="I1" s="11"/>
       <c r="J1" s="12" t="s">
         <v>126</v>
@@ -3810,35 +3790,35 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="38" t="str">
+      <c r="A2" s="72" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="31"/>
+      <c r="K2" s="35"/>
     </row>
     <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="38" t="str">
+      <c r="A3" s="72" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
@@ -3848,17 +3828,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="38" t="str">
+      <c r="A4" s="72" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
@@ -3868,16 +3848,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="73" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
@@ -3930,13 +3910,13 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
       <c r="F8" s="11"/>
       <c r="G8" s="18" t="s">
         <v>137</v>
@@ -3954,13 +3934,13 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
@@ -3987,123 +3967,123 @@
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="45" t="s">
+      <c r="B11" s="64"/>
+      <c r="C11" s="63" t="s">
         <v>153</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="45" t="str">
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="63" t="str">
         <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
         <v>AMOUNT (MYR)</v>
       </c>
-      <c r="H11" s="46"/>
+      <c r="H11" s="64"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="44">
+      <c r="A12" s="62">
         <v>1</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="43" t="s">
+      <c r="B12" s="35"/>
+      <c r="C12" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="42">
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="66">
         <v>9000</v>
       </c>
-      <c r="H12" s="31"/>
+      <c r="H12" s="35"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="44"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="31"/>
+      <c r="A13" s="62"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="35"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="44"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="31"/>
+      <c r="A14" s="62"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="35"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="44"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="31"/>
+      <c r="A15" s="62"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="35"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="44"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="31"/>
+      <c r="A16" s="62"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="35"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="44"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="31"/>
+      <c r="A17" s="62"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="69" t="s">
         <v>155</v>
       </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="47">
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="67">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
-      <c r="H18" s="31"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -4126,15 +4106,15 @@
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="71" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -4153,32 +4133,32 @@
       <c r="K21" s="11"/>
     </row>
     <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="68" t="s">
         <v>156</v>
       </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="48" t="str">
+      <c r="A23" s="68" t="str">
         <f>IF($K$3="","","Bank : "&amp;IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),""))</f>
         <v>Bank : Malayan Banking Berhad (Maybank)</v>
       </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -4197,16 +4177,16 @@
       <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="58" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -4278,25 +4258,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="G17:H17"/>
@@ -4313,15 +4274,34 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>"BOC,BOCOM,MBB,OCBC,TBC,UOB"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
-  <pageSetup paperSize="11" scale="67" orientation="landscape" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.3" bottom="0.3" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="96" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -4357,17 +4337,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="33" t="str">
+      <c r="A1" s="70" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
       <c r="I1" s="11"/>
       <c r="J1" s="12" t="s">
         <v>126</v>
@@ -4375,35 +4355,35 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="38" t="str">
+      <c r="A2" s="72" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="31"/>
+      <c r="K2" s="35"/>
     </row>
     <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="38" t="str">
+      <c r="A3" s="72" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
@@ -4413,17 +4393,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="38" t="str">
+      <c r="A4" s="72" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
@@ -4433,16 +4413,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
@@ -4495,13 +4475,13 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
       <c r="F8" s="11"/>
       <c r="G8" s="18" t="s">
         <v>137</v>
@@ -4519,13 +4499,13 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
@@ -4552,123 +4532,123 @@
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="45" t="s">
+      <c r="B11" s="64"/>
+      <c r="C11" s="63" t="s">
         <v>153</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="45" t="str">
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="63" t="str">
         <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
         <v>AMOUNT (MYR)</v>
       </c>
-      <c r="H11" s="46"/>
+      <c r="H11" s="64"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="44">
+      <c r="A12" s="62">
         <v>1</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="43" t="s">
+      <c r="B12" s="35"/>
+      <c r="C12" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="42">
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="66">
         <v>9000</v>
       </c>
-      <c r="H12" s="31"/>
+      <c r="H12" s="35"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="44"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="31"/>
+      <c r="A13" s="62"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="35"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="44"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="31"/>
+      <c r="A14" s="62"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="35"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="44"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="31"/>
+      <c r="A15" s="62"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="35"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="44"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="31"/>
+      <c r="A16" s="62"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="35"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="44"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="31"/>
+      <c r="A17" s="62"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="69" t="s">
         <v>155</v>
       </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="47">
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="67">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
-      <c r="H18" s="31"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -4691,15 +4671,15 @@
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="71" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -4722,12 +4702,12 @@
         <v>161</v>
       </c>
       <c r="B22" s="11"/>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -4739,13 +4719,13 @@
         <v>163</v>
       </c>
       <c r="B23" s="11"/>
-      <c r="C23" s="52" t="str">
+      <c r="C23" s="76" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
@@ -4757,12 +4737,12 @@
         <v>164</v>
       </c>
       <c r="B24" s="11"/>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="75" t="s">
         <v>165</v>
       </c>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
@@ -4783,16 +4763,16 @@
       <c r="K25" s="11"/>
     </row>
     <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="74" t="s">
         <v>166</v>
       </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -4811,16 +4791,16 @@
       <c r="K27" s="11"/>
     </row>
     <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="58" t="s">
         <v>157</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -4853,6 +4833,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="A28:H28"/>
@@ -4869,36 +4870,15 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0600-000001000000}">
       <formula1>"BOC,BOCOM,MBB,OCBC,TBC,UOB"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
-  <pageSetup paperSize="11" scale="59" orientation="landscape" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.3" bottom="0.3" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="96" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -4934,16 +4914,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="33" t="str">
+      <c r="A1" s="70" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
       <c r="H1" s="11"/>
       <c r="I1" s="11"/>
       <c r="J1" s="12" t="s">
@@ -4952,34 +4932,34 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="38" t="str">
+      <c r="A2" s="72" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="31"/>
+      <c r="K2" s="35"/>
     </row>
     <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="38" t="str">
+      <c r="A3" s="72" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
       <c r="H3" s="11"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
@@ -4990,16 +4970,16 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="38" t="str">
+      <c r="A4" s="72" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
@@ -5010,16 +4990,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
@@ -5050,18 +5030,18 @@
       <c r="A7" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="75" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="31"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="11"/>
       <c r="E7" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="75" t="s">
         <v>171</v>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="15" t="s">
@@ -5076,18 +5056,18 @@
       <c r="A8" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="31"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="11"/>
       <c r="E8" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="F8" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="31"/>
+      <c r="G8" s="35"/>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="15" t="s">
@@ -5106,11 +5086,11 @@
       <c r="E9" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="F9" s="54" t="str">
+      <c r="F9" s="78" t="str">
         <f>K7</f>
         <v>SAL/NEK/BOC/202607/014</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="10" t="s">
@@ -5121,17 +5101,17 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="77" t="s">
         <v>177</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="57" t="s">
+      <c r="E10" s="77" t="s">
         <v>178</v>
       </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
@@ -5247,11 +5227,11 @@
       <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="77" t="s">
         <v>186</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
@@ -5390,11 +5370,11 @@
       <c r="K23" s="11"/>
     </row>
     <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A24" s="57" t="s">
+      <c r="A24" s="77" t="s">
         <v>193</v>
       </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
@@ -5478,15 +5458,15 @@
       <c r="K28" s="11"/>
     </row>
     <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
@@ -5507,6 +5487,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="A24:C24"/>
@@ -5515,23 +5503,15 @@
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="E10:G10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0700-000001000000}">
       <formula1>"BOC,BOCOM,MBB,OCBC,TBC,UOB"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.15" footer="0.15"/>
-  <pageSetup paperSize="11" scale="58" orientation="landscape" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.3" bottom="0.3" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">

--- a/templates/NEK_Document_Templates.xlsx
+++ b/templates/NEK_Document_Templates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude Cowork\NEK\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C840434-6C31-4BAB-BBED-CF05EB567690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6BE01EA-94BE-419A-A217-21CD63A5E849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="211">
   <si>
     <t>NEK GROUP — DOCUMENT HOUSE STYLE</t>
   </si>
@@ -488,9 +488,6 @@
     <t>RECEIVING VOUCHER</t>
   </si>
   <si>
-    <t>RECEIVED FM :</t>
-  </si>
-  <si>
     <t>RV NO :</t>
   </si>
   <si>
@@ -678,6 +675,12 @@
   </si>
   <si>
     <t>CHECKED BY</t>
+  </si>
+  <si>
+    <t>RECEIVED FROM :</t>
+  </si>
+  <si>
+    <t>BEING PAYMENT FOR</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1265,33 +1268,89 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="27" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="29" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="27" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1299,78 +1358,54 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1380,43 +1415,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1952,18 +1951,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B2" t="s">
         <v>198</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>199</v>
-      </c>
-      <c r="C2" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1971,10 +1970,10 @@
         <v>90</v>
       </c>
       <c r="B3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" t="s">
         <v>201</v>
-      </c>
-      <c r="C3" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1982,10 +1981,10 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" t="s">
         <v>203</v>
-      </c>
-      <c r="C4" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1993,10 +1992,10 @@
         <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2616,17 +2615,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="50" t="str">
+      <c r="A1" s="52" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
       <c r="I1" s="11"/>
       <c r="J1" s="12" t="s">
         <v>126</v>
@@ -2634,35 +2633,35 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="10" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="40" t="str">
+      <c r="A2" s="65" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="63" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="35"/>
+      <c r="K2" s="38"/>
     </row>
     <row r="3" spans="1:11" ht="10" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="40" t="str">
+      <c r="A3" s="65" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
@@ -2672,17 +2671,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="40" t="str">
+      <c r="A4" s="65" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
@@ -2692,16 +2691,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="68" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
@@ -2732,20 +2731,20 @@
       <c r="A7" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="87" t="s">
+      <c r="B7" s="58" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="56"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="86" t="s">
+      <c r="C7" s="59"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="G7" s="89" t="str">
+      <c r="G7" s="70" t="str">
         <f>K7</f>
         <v>PV/NEK/BOC/202607/014</v>
       </c>
-      <c r="H7" s="90"/>
+      <c r="H7" s="71"/>
       <c r="I7" s="11"/>
       <c r="J7" s="15" t="s">
         <v>134</v>
@@ -2761,13 +2760,13 @@
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
-      <c r="F8" s="86" t="s">
-        <v>207</v>
-      </c>
-      <c r="G8" s="91" t="s">
+      <c r="F8" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="G8" s="61" t="s">
         <v>135</v>
       </c>
-      <c r="H8" s="92"/>
+      <c r="H8" s="62"/>
       <c r="I8" s="11"/>
       <c r="J8" s="15" t="s">
         <v>136</v>
@@ -2783,16 +2782,16 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
-      <c r="F9" s="86" t="s">
+      <c r="F9" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="57">
+      <c r="G9" s="35">
         <v>46228</v>
       </c>
-      <c r="H9" s="93"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K9" s="11" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
@@ -2813,121 +2812,121 @@
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="45" t="str">
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="66" t="str">
         <f>$K$9</f>
         <v>MYR</v>
       </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="45" t="s">
+      <c r="F11" s="56"/>
+      <c r="G11" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="47"/>
+      <c r="H11" s="67"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="42">
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="45">
         <v>2793</v>
       </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="47"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="38"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
+      <c r="A13" s="41"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="47"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="38"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
+      <c r="A14" s="41"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="47"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="38"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="44"/>
+      <c r="A15" s="41"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="47"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="38"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="44"/>
+      <c r="A16" s="41"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="47"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="38"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="44"/>
+      <c r="A17" s="41"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="47"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="36">
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="64">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="55"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="57"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -2946,17 +2945,17 @@
       <c r="K19" s="11"/>
     </row>
     <row r="20" spans="1:11" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="81" t="str">
+      <c r="A20" s="34" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="82"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="84"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="51"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -2991,15 +2990,15 @@
       <c r="A23" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="52"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="11"/>
       <c r="E23" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
+        <v>207</v>
+      </c>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -3019,17 +3018,17 @@
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="52"/>
+        <v>208</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="11"/>
       <c r="E25" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="F25" s="60"/>
-      <c r="G25" s="60"/>
-      <c r="H25" s="60"/>
+        <v>207</v>
+      </c>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -3051,15 +3050,15 @@
       <c r="A27" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="52"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="11"/>
       <c r="E27" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="F27" s="60"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
+        <v>207</v>
+      </c>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
@@ -3091,30 +3090,36 @@
       <c r="K29" s="11"/>
     </row>
     <row r="30" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="58"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="E17:F17"/>
@@ -3131,22 +3136,16 @@
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B20:H20"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -3194,17 +3193,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="50" t="str">
+      <c r="A1" s="52" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
       <c r="I1" s="11"/>
       <c r="J1" s="12" t="s">
         <v>126</v>
@@ -3212,35 +3211,35 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="10" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="40" t="str">
+      <c r="A2" s="65" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="63" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="35"/>
+      <c r="K2" s="38"/>
     </row>
     <row r="3" spans="1:11" ht="10" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="40" t="str">
+      <c r="A3" s="65" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
@@ -3250,17 +3249,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="40" t="str">
+      <c r="A4" s="65" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
@@ -3270,16 +3269,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
@@ -3308,22 +3307,22 @@
     </row>
     <row r="7" spans="1:11" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="59"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="B7" s="87" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="56"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="86" t="s">
-        <v>147</v>
-      </c>
-      <c r="G7" s="89" t="str">
+      <c r="G7" s="70" t="str">
         <f>K7</f>
         <v>RV/NEK/BOC/202607/014</v>
       </c>
-      <c r="H7" s="90"/>
+      <c r="H7" s="71"/>
       <c r="I7" s="11"/>
       <c r="J7" s="15" t="s">
         <v>134</v>
@@ -3339,13 +3338,13 @@
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
-      <c r="F8" s="86" t="s">
-        <v>207</v>
-      </c>
-      <c r="G8" s="91" t="s">
+      <c r="F8" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="G8" s="61" t="s">
         <v>135</v>
       </c>
-      <c r="H8" s="92"/>
+      <c r="H8" s="62"/>
       <c r="I8" s="11"/>
       <c r="J8" s="15" t="s">
         <v>136</v>
@@ -3361,16 +3360,16 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
-      <c r="F9" s="86" t="s">
+      <c r="F9" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="57">
+      <c r="G9" s="35">
         <v>46228</v>
       </c>
-      <c r="H9" s="93"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K9" s="11" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
@@ -3391,121 +3390,121 @@
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="13" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="54" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="45" t="str">
+      <c r="A11" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="66" t="str">
         <f>$K$9</f>
         <v>MYR</v>
       </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="45" t="s">
+      <c r="F11" s="56"/>
+      <c r="G11" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="H11" s="47"/>
+      <c r="H11" s="67"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="42">
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="45">
         <v>2793</v>
       </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="44"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="47"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="38"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
+      <c r="A13" s="41"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="47"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="38"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="44"/>
+      <c r="A14" s="41"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="47"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="38"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="44"/>
+      <c r="A15" s="41"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="47"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="38"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="44"/>
+      <c r="A16" s="41"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="47"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="38"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="44"/>
+      <c r="A17" s="41"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="47"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="36">
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="64">
         <f>SUM(E12:F17)</f>
         <v>2793</v>
       </c>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="55"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="57"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -3524,17 +3523,17 @@
       <c r="K19" s="11"/>
     </row>
     <row r="20" spans="1:11" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="81" t="str">
+      <c r="A20" s="34" t="str">
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="82"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="84"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="51"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -3569,15 +3568,15 @@
       <c r="A23" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="52"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="11"/>
       <c r="E23" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
+        <v>207</v>
+      </c>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -3597,17 +3596,17 @@
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="52"/>
+        <v>208</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="11"/>
       <c r="E25" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="F25" s="60"/>
-      <c r="G25" s="60"/>
-      <c r="H25" s="60"/>
+        <v>207</v>
+      </c>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -3629,15 +3628,15 @@
       <c r="A27" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="52"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="11"/>
       <c r="E27" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="F27" s="60"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
+        <v>207</v>
+      </c>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
@@ -3669,30 +3668,36 @@
       <c r="K29" s="11"/>
     </row>
     <row r="30" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="58"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="E17:F17"/>
@@ -3709,22 +3714,16 @@
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="B20:H20"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0400-000001000000}">
@@ -3772,17 +3771,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="70" t="str">
+      <c r="A1" s="72" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
       <c r="I1" s="11"/>
       <c r="J1" s="12" t="s">
         <v>126</v>
@@ -3790,35 +3789,35 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="72" t="str">
+      <c r="A2" s="77" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="63" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="35"/>
+      <c r="K2" s="38"/>
     </row>
     <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="72" t="str">
+      <c r="A3" s="77" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
@@ -3828,17 +3827,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="72" t="str">
+      <c r="A4" s="77" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
@@ -3848,16 +3847,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="73" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
+      <c r="A5" s="80" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
@@ -3886,7 +3885,7 @@
     </row>
     <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -3894,7 +3893,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H7" s="21" t="str">
         <f>K7</f>
@@ -3910,13 +3909,13 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="61" t="s">
+      <c r="A8" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
       <c r="F8" s="11"/>
       <c r="G8" s="18" t="s">
         <v>137</v>
@@ -3934,19 +3933,19 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="65" t="s">
-        <v>151</v>
-      </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
+      <c r="A9" s="84" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K9" s="11" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
@@ -3967,123 +3966,123 @@
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="79"/>
+      <c r="C11" s="78" t="s">
         <v>152</v>
       </c>
-      <c r="B11" s="64"/>
-      <c r="C11" s="63" t="s">
-        <v>153</v>
-      </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="63" t="str">
+      <c r="D11" s="79"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="78" t="str">
         <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
         <v>AMOUNT (MYR)</v>
       </c>
-      <c r="H11" s="64"/>
+      <c r="H11" s="79"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="62">
+      <c r="A12" s="76">
         <v>1</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="61" t="s">
-        <v>154</v>
-      </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="66">
+      <c r="B12" s="38"/>
+      <c r="C12" s="75" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="74">
         <v>9000</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="38"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="62"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="35"/>
+      <c r="A13" s="76"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="38"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="62"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="35"/>
+      <c r="A14" s="76"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="38"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="62"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="35"/>
+      <c r="A15" s="76"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="38"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="62"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="35"/>
+      <c r="A16" s="76"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="38"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="62"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="35"/>
+      <c r="A17" s="76"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="38"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="69" t="s">
-        <v>155</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="67">
+      <c r="A18" s="83" t="s">
+        <v>154</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="81">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
-      <c r="H18" s="35"/>
+      <c r="H18" s="38"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -4106,15 +4105,15 @@
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="73" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -4133,32 +4132,32 @@
       <c r="K21" s="11"/>
     </row>
     <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A22" s="68" t="s">
-        <v>156</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
+      <c r="A22" s="82" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="68" t="str">
+      <c r="A23" s="82" t="str">
         <f>IF($K$3="","","Bank : "&amp;IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),""))</f>
         <v>Bank : Malayan Banking Berhad (Maybank)</v>
       </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -4177,16 +4176,16 @@
       <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="58" t="s">
-        <v>157</v>
-      </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
+      <c r="A25" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -4258,6 +4257,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="G17:H17"/>
@@ -4274,25 +4292,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0500-000001000000}">
@@ -4337,17 +4336,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="70" t="str">
+      <c r="A1" s="72" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
       <c r="I1" s="11"/>
       <c r="J1" s="12" t="s">
         <v>126</v>
@@ -4355,35 +4354,35 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="72" t="str">
+      <c r="A2" s="77" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="63" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="35"/>
+      <c r="K2" s="38"/>
     </row>
     <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="72" t="str">
+      <c r="A3" s="77" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
         <v>52</v>
@@ -4393,17 +4392,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="72" t="str">
+      <c r="A4" s="77" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
         <v>98</v>
@@ -4413,16 +4412,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="73" t="s">
-        <v>158</v>
-      </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
+      <c r="A5" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
@@ -4451,7 +4450,7 @@
     </row>
     <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -4459,7 +4458,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H7" s="21" t="str">
         <f>K7</f>
@@ -4475,13 +4474,13 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="61" t="s">
+      <c r="A8" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
       <c r="F8" s="11"/>
       <c r="G8" s="18" t="s">
         <v>137</v>
@@ -4499,19 +4498,19 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="65" t="s">
-        <v>151</v>
-      </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
+      <c r="A9" s="84" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K9" s="11" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$E$3:$E$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
@@ -4532,123 +4531,123 @@
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="79"/>
+      <c r="C11" s="78" t="s">
         <v>152</v>
       </c>
-      <c r="B11" s="64"/>
-      <c r="C11" s="63" t="s">
-        <v>153</v>
-      </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="63" t="str">
+      <c r="D11" s="79"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="78" t="str">
         <f>IF($K$9="","AMOUNT","AMOUNT ("&amp;$K$9&amp;")")</f>
         <v>AMOUNT (MYR)</v>
       </c>
-      <c r="H11" s="64"/>
+      <c r="H11" s="79"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="62">
+      <c r="A12" s="76">
         <v>1</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="61" t="s">
-        <v>154</v>
-      </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="66">
+      <c r="B12" s="38"/>
+      <c r="C12" s="75" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="74">
         <v>9000</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="38"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="62"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="35"/>
+      <c r="A13" s="76"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="38"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="62"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="35"/>
+      <c r="A14" s="76"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="38"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
     </row>
     <row r="15" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="62"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="35"/>
+      <c r="A15" s="76"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="38"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="62"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="35"/>
+      <c r="A16" s="76"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="38"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
     </row>
     <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="62"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="35"/>
+      <c r="A17" s="76"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="38"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="69" t="s">
-        <v>155</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="67">
+      <c r="A18" s="83" t="s">
+        <v>154</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="81">
         <f>SUM(G12:H17)</f>
         <v>9000</v>
       </c>
-      <c r="H18" s="35"/>
+      <c r="H18" s="38"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -4671,15 +4670,15 @@
         <f>IF($K$9="","",IFERROR(INDEX(_Currency!$B$3:$B$20,MATCH($K$9,_Currency!$A$3:$A$20,0)),$K$9)&amp;" :")</f>
         <v>Ringgit Malaysia :</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="73" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -4699,15 +4698,15 @@
     </row>
     <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
       <c r="A22" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="85" t="s">
         <v>161</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="75" t="s">
-        <v>162</v>
-      </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -4716,16 +4715,16 @@
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B23" s="11"/>
-      <c r="C23" s="76" t="str">
+      <c r="C23" s="86" t="str">
         <f>IFERROR(INDEX(_BankAccounts!$D$3:$D$100,MATCH($K$3&amp;"|"&amp;$K$4,_BankAccounts!$A$3:$A$100,0)),"")</f>
         <v>Bank of China (Malaysia) Berhad</v>
       </c>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
@@ -4734,15 +4733,15 @@
     </row>
     <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
       <c r="A24" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="75" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
@@ -4763,16 +4762,16 @@
       <c r="K25" s="11"/>
     </row>
     <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A26" s="74" t="s">
-        <v>166</v>
-      </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
+      <c r="A26" s="87" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -4791,16 +4790,16 @@
       <c r="K27" s="11"/>
     </row>
     <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A28" s="58" t="s">
-        <v>157</v>
-      </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
+      <c r="A28" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -4833,6 +4832,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B20:H20"/>
@@ -4849,27 +4869,6 @@
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="A4:H4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0600-000001000000}">
@@ -4914,16 +4913,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="70" t="str">
+      <c r="A1" s="72" t="str">
         <f>IFERROR(INDEX(_EntityData!$B$3:$B$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>Ng Eng Kee &amp; Sons Sdn Bhd</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
       <c r="H1" s="11"/>
       <c r="I1" s="11"/>
       <c r="J1" s="12" t="s">
@@ -4932,34 +4931,34 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="72" t="str">
+      <c r="A2" s="77" t="str">
         <f>IF($K$3="","",IFERROR(IF(INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))="","","Co. Reg. No. "&amp;INDEX(_EntityData!$C$3:$C$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))),""))</f>
         <v>Co. Reg. No. 198401003022 (115540-H)</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="63" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="35"/>
+      <c r="K2" s="38"/>
     </row>
     <row r="3" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="72" t="str">
+      <c r="A3" s="77" t="str">
         <f>IF($K$3="","",IFERROR("Tel: "&amp;INDEX(_EntityData!$F$3:$F$100,MATCH($K$3,_EntityData!$A$3:$A$100,0))&amp;"      Email: "&amp;INDEX(_EntityData!$G$3:$G$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),""))</f>
         <v>Tel: 012-4820853      Email: nekgroup84@gmail.com</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
       <c r="H3" s="11"/>
       <c r="I3" s="11"/>
       <c r="J3" s="10" t="s">
@@ -4970,16 +4969,16 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="72" t="str">
+      <c r="A4" s="77" t="str">
         <f>IFERROR(INDEX(_EntityData!$D$3:$D$100,MATCH($K$3,_EntityData!$A$3:$A$100,0)),"")</f>
         <v>51-10-E, Menara BHL, Jalan Sultan Ahmad Shah, 10050 Georgetown, Penang, Malaysia</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="10" t="s">
@@ -4990,16 +4989,16 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="79" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
+      <c r="A5" s="89" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
       <c r="I5" s="11"/>
       <c r="J5" s="10" t="s">
         <v>129</v>
@@ -5028,20 +5027,20 @@
     </row>
     <row r="7" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" s="85" t="s">
         <v>168</v>
       </c>
-      <c r="B7" s="75" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="35"/>
+      <c r="C7" s="38"/>
       <c r="D7" s="11"/>
       <c r="E7" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="F7" s="85" t="s">
         <v>170</v>
       </c>
-      <c r="F7" s="75" t="s">
-        <v>171</v>
-      </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="38"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="15" t="s">
@@ -5054,20 +5053,20 @@
     </row>
     <row r="8" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="85" t="s">
         <v>172</v>
       </c>
-      <c r="B8" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="35"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="11"/>
       <c r="E8" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="F8" s="62" t="s">
+        <v>173</v>
+      </c>
+      <c r="F8" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="35"/>
+      <c r="G8" s="38"/>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="15" t="s">
@@ -5084,34 +5083,34 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F9" s="78" t="str">
+        <v>174</v>
+      </c>
+      <c r="F9" s="88" t="str">
         <f>K7</f>
         <v>SAL/NEK/BOC/202607/014</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="38"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K9" s="23">
         <v>46228</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="91" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="91" t="s">
         <v>177</v>
       </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="77" t="s">
-        <v>178</v>
-      </c>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
@@ -5119,7 +5118,7 @@
     </row>
     <row r="11" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>63</v>
@@ -5129,7 +5128,7 @@
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F11" s="24" t="s">
         <v>63</v>
@@ -5144,7 +5143,7 @@
     </row>
     <row r="12" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>63</v>
@@ -5154,7 +5153,7 @@
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F12" s="24" t="s">
         <v>63</v>
@@ -5173,7 +5172,7 @@
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F13" s="24" t="s">
         <v>63</v>
@@ -5188,7 +5187,7 @@
     </row>
     <row r="14" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>63</v>
@@ -5199,7 +5198,7 @@
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>63</v>
@@ -5227,11 +5226,11 @@
       <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="77" t="s">
-        <v>186</v>
-      </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
+      <c r="A16" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
@@ -5243,7 +5242,7 @@
     </row>
     <row r="17" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>63</v>
@@ -5262,7 +5261,7 @@
     </row>
     <row r="18" spans="1:11" ht="22" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>63</v>
@@ -5281,7 +5280,7 @@
     </row>
     <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.4">
       <c r="A19" s="24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>63</v>
@@ -5300,7 +5299,7 @@
     </row>
     <row r="20" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>63</v>
@@ -5319,7 +5318,7 @@
     </row>
     <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.4">
       <c r="A21" s="24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B21" s="24" t="s">
         <v>63</v>
@@ -5338,7 +5337,7 @@
     </row>
     <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.4">
       <c r="A22" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>63</v>
@@ -5370,11 +5369,11 @@
       <c r="K23" s="11"/>
     </row>
     <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A24" s="77" t="s">
-        <v>193</v>
-      </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
+      <c r="A24" s="91" t="s">
+        <v>192</v>
+      </c>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
@@ -5386,7 +5385,7 @@
     </row>
     <row r="25" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>63</v>
@@ -5406,7 +5405,7 @@
     </row>
     <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.4">
       <c r="A26" s="24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>63</v>
@@ -5426,7 +5425,7 @@
     </row>
     <row r="27" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B27" s="28" t="s">
         <v>63</v>
@@ -5458,15 +5457,15 @@
       <c r="K28" s="11"/>
     </row>
     <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.4">
-      <c r="A29" s="58" t="s">
-        <v>196</v>
-      </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
+      <c r="A29" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
@@ -5487,6 +5486,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="E10:G10"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="F9:G9"/>
@@ -5495,14 +5502,6 @@
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="E10:G10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="K4" xr:uid="{00000000-0002-0000-0700-000001000000}">
